--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Reg 0x00: OUT=0x0001, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x00: OUT=0x8000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:50</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:50</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:50</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:43</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:44</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:52</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:45</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Reg 0x20: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x20: OUT=0xD080, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Reg 0x21: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x21: OUT=0xD585, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:53</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:46</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Reg 0x28: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x28: OUT=0x1FBF, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Reg 0x29: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x29: OUT=0x000F, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Reg 0x2A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x2A: OUT=0x0D0D, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:54</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:47</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Reg 0x33: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x33: OUT=0x0002, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:55</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:48</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:56</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:49</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:57</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:50</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4673,16 +4673,16 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Reg 0x57: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x57: OUT=0x0008, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -4721,16 +4721,16 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Reg 0x58: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x58: OUT=0x0004, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -4769,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:58</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Reg 0x59: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x59: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -4817,16 +4817,16 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Reg 0x5A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x5A: OUT=0x0064, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -4865,16 +4865,16 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:51</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Reg 0x5B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x5B: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -4913,16 +4913,16 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Reg 0x5C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x5C: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -4961,16 +4961,16 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Reg 0x5D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x5D: OUT=0xFE0C, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5009,16 +5009,16 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Reg 0x5E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x5E: OUT=0x1B58, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Reg 0x5F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x5F: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5105,16 +5105,16 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Reg 0x60: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x60: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5153,16 +5153,16 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Reg 0x61: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x61: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5249,16 +5249,16 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:04:59</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Reg 0x63: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x63: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5297,16 +5297,16 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Reg 0x64: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x64: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:52</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5537,16 +5537,16 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Reg 0x69: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x69: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5585,16 +5585,16 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Reg 0x6A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x6A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5633,16 +5633,16 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Reg 0x6B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x6B: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:00</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:53</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:01</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:54</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:02</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:55</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Reg 0x89: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x89: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Reg 0x8A: OUT=0x0014, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8A: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Reg 0x8B: OUT=0x001E, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8B: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:03</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:56</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7505,16 +7505,16 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Reg 0x92: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+          <t>Reg 0x92: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:04</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:57</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:05</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:58</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:06</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-11 11:39:59</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:07</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:00</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:08</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:01</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:09</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:02</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:10</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:03</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:11</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:04</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:12</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:05</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:13</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:06</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:07</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:07</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:07</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:07</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026-03-11 11:40:07</t>
+          <t>2026-03-11 15:05:14</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">

--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J257"/>
+  <dimension ref="A1:K257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,25 +458,30 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>OverallResult</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tester</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Test Suite</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -506,27 +511,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:50</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Reg 0x00: OUT=0x8000, CE=0, STATUS=0 (OK)</t>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Reg 0x00: OUT=0x8001, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -554,25 +564,30 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:50</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Reg 0x01: OUT=0x0008, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -602,25 +617,30 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:50</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Reg 0x02: OUT=0x0010, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -650,25 +670,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:50</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Reg 0x03: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -698,25 +723,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Reg 0x04: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -746,25 +776,30 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Reg 0x05: OUT=0x000B, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -794,25 +829,30 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Reg 0x06: OUT=0x0006, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -842,25 +882,30 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Reg 0x07: OUT=0x0006, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -890,25 +935,30 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Reg 0x08: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -938,25 +988,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Reg 0x09: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -986,25 +1041,30 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Reg 0x0A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1034,25 +1094,30 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Reg 0x0B: OUT=0x312E, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1082,25 +1147,30 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Reg 0x0C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1130,25 +1200,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Reg 0x0D: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1178,25 +1253,30 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:51</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Reg 0x0E: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1226,25 +1306,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Reg 0x0F: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1274,25 +1359,30 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Reg 0x10: OUT=0x312E, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1322,25 +1412,30 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Reg 0x11: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1370,25 +1465,30 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Reg 0x12: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1418,25 +1518,30 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Reg 0x13: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1466,25 +1571,30 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Reg 0x14: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1514,25 +1624,30 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Reg 0x15: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -1562,25 +1677,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Reg 0x16: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1610,25 +1730,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Reg 0x17: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1658,25 +1783,30 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:26</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Reg 0x18: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1706,25 +1836,30 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:52</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Reg 0x19: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1754,25 +1889,30 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Reg 0x1A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1802,25 +1942,30 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Reg 0x1B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1850,25 +1995,30 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Reg 0x1C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1898,25 +2048,30 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Reg 0x1D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1946,25 +2101,30 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Reg 0x1E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -1994,25 +2154,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Reg 0x1F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -2042,25 +2207,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Reg 0x20: OUT=0xD080, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2090,25 +2260,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Reg 0x21: OUT=0xD585, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2138,25 +2313,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Reg 0x22: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2186,25 +2366,30 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:53</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:27</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Reg 0x23: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2234,25 +2419,30 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Reg 0x24: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2282,25 +2472,30 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Reg 0x25: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2330,25 +2525,30 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Reg 0x26: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2378,25 +2578,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Reg 0x27: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2426,25 +2631,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Reg 0x28: OUT=0x1FBF, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2474,25 +2684,30 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Reg 0x29: OUT=0x000F, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2522,25 +2737,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Reg 0x2A: OUT=0x0D0D, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2570,25 +2790,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Reg 0x2B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -2618,25 +2843,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Reg 0x2C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -2666,25 +2896,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:28</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Reg 0x2D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -2714,25 +2949,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:54</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Reg 0x2E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -2762,25 +3002,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Reg 0x2F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -2810,25 +3055,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Reg 0x30: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2858,25 +3108,30 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Reg 0x31: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2906,25 +3161,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Reg 0x32: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -2954,25 +3214,30 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Reg 0x33: OUT=0x0002, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3002,25 +3267,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Reg 0x34: OUT=0x01F4, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3050,25 +3320,30 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Reg 0x35: OUT=0x00C1, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3098,25 +3373,30 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Reg 0x36: OUT=0x1194, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3146,25 +3426,30 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Reg 0x37: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3194,25 +3479,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:29</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Reg 0x38: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3242,25 +3532,30 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:55</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Reg 0x39: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3290,25 +3585,30 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Reg 0x3A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3338,25 +3638,30 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Reg 0x3B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3386,25 +3691,30 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Reg 0x3C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3434,25 +3744,30 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Reg 0x3D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3482,25 +3797,30 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Reg 0x3E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3530,25 +3850,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Reg 0x3F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3578,25 +3903,30 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Reg 0x40: OUT=0x00C1, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3626,25 +3956,30 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Reg 0x41: OUT=0x1194, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3674,25 +4009,30 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Reg 0x42: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3722,25 +4062,30 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:56</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Reg 0x43: OUT=0x09C4, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -3770,25 +4115,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Reg 0x44: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3818,25 +4168,30 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Reg 0x45: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3866,25 +4221,30 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Reg 0x46: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3914,25 +4274,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Reg 0x47: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -3962,25 +4327,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>Reg 0x48: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4010,25 +4380,30 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Reg 0x49: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4058,25 +4433,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Reg 0x4A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4106,25 +4486,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Reg 0x4B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4154,25 +4539,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>Reg 0x4C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4202,25 +4592,30 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>Reg 0x4D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4250,25 +4645,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:57</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>Reg 0x4E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -4298,25 +4698,30 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>Reg 0x4F: OUT=0x1388, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4346,25 +4751,30 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>Reg 0x50: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4394,25 +4804,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>Reg 0x51: OUT=0x07D0, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4442,25 +4857,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>Reg 0x52: OUT=0x00C1, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4490,25 +4910,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>Reg 0x53: OUT=0x1194, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4538,25 +4963,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>Reg 0x54: OUT=0x00C6, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4586,25 +5016,30 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>Reg 0x55: OUT=0x1194, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4634,25 +5069,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>Reg 0x56: OUT=0x00FA, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4682,25 +5122,30 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>Reg 0x57: OUT=0x0008, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4730,25 +5175,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:32</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>Reg 0x58: OUT=0x0004, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4778,25 +5228,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:58</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Reg 0x59: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4826,25 +5281,30 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>Reg 0x5A: OUT=0x0064, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4874,25 +5334,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Reg 0x5B: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4922,25 +5387,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>Reg 0x5C: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -4970,25 +5440,30 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>Reg 0x5D: OUT=0xFE0C, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5018,25 +5493,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>Reg 0x5E: OUT=0x1B58, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5066,25 +5546,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>Reg 0x5F: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5114,25 +5599,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>Reg 0x60: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5162,25 +5652,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>Reg 0x61: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5210,25 +5705,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>Reg 0x62: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5258,25 +5758,30 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-11 15:04:59</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:33</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>Reg 0x63: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5306,25 +5811,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>Reg 0x64: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5354,25 +5864,30 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>Reg 0x65: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5402,25 +5917,30 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>Reg 0x66: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5450,25 +5970,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>Reg 0x67: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5498,25 +6023,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>Reg 0x68: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5546,25 +6076,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>Reg 0x69: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5594,25 +6129,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>Reg 0x6A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5642,25 +6182,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>Reg 0x6B: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -5690,25 +6235,30 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>Reg 0x6C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -5738,25 +6288,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:34</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>Reg 0x6D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -5786,25 +6341,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:00</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>Reg 0x6E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -5834,25 +6394,30 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>Reg 0x6F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -5882,25 +6447,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>Reg 0x70: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -5930,25 +6500,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>Reg 0x71: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -5978,25 +6553,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>Reg 0x72: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6026,25 +6606,30 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>Reg 0x73: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6074,25 +6659,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>Reg 0x74: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6122,25 +6712,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>Reg 0x75: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6170,25 +6765,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>Reg 0x76: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6218,25 +6818,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>Reg 0x77: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6266,25 +6871,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:35</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>Reg 0x78: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6314,25 +6924,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:01</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>Reg 0x79: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6362,25 +6977,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>Reg 0x7A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6410,25 +7030,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>Reg 0x7B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6458,25 +7083,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Reg 0x7C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6506,25 +7136,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>Reg 0x7D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6554,25 +7189,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>Reg 0x7E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6602,25 +7242,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>Reg 0x7F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -6650,25 +7295,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>Reg 0x80: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6698,25 +7348,30 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>Reg 0x81: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6746,25 +7401,30 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:36</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>Reg 0x82: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6794,25 +7454,30 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:02</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>Reg 0x83: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6842,25 +7507,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>Reg 0x84: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6890,25 +7560,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>Reg 0x85: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6938,25 +7613,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>Reg 0x86: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -6986,25 +7666,30 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>Reg 0x87: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7034,25 +7719,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>Reg 0x88: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7082,27 +7772,32 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Reg 0x89: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Reg 0x89: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7130,27 +7825,32 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Reg 0x8A: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Reg 0x8A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7178,25 +7878,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>Reg 0x8B: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7226,25 +7931,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>Reg 0x8C: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7274,25 +7984,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:37</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>Reg 0x8D: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7322,25 +8037,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:03</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>Reg 0x8E: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7370,25 +8090,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>Reg 0x8F: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7418,25 +8143,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>Reg 0x90: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7466,25 +8196,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>Reg 0x91: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7514,25 +8249,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Rishi</t>
-        </is>
-      </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>Reg 0x92: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
@@ -7562,25 +8302,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>Reg 0x93: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7610,25 +8355,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>Reg 0x94: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7658,25 +8408,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>Reg 0x95: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7706,25 +8461,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>Reg 0x96: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7754,25 +8514,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Reg 0x97: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7802,25 +8567,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:38</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>Reg 0x98: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7850,25 +8620,30 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:04</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>Reg 0x99: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7898,25 +8673,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>Reg 0x9A: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7946,25 +8726,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>Reg 0x9B: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -7994,25 +8779,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>Reg 0x9C: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8042,25 +8832,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>Reg 0x9D: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8090,25 +8885,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>Reg 0x9E: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8138,25 +8938,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>Reg 0x9F: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8186,25 +8991,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>Reg 0xA0: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8234,25 +9044,30 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>Reg 0xA1: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8282,25 +9097,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:39</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>Reg 0xA2: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8330,25 +9150,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:05</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>Reg 0xA3: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8378,25 +9203,30 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>Reg 0xA4: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8426,25 +9256,30 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>Reg 0xA5: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8474,25 +9309,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>Reg 0xA6: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8522,25 +9362,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
         <is>
           <t>Reg 0xA7: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8570,25 +9415,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
         <is>
           <t>Reg 0xA8: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8618,25 +9468,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>Reg 0xA9: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8666,25 +9521,30 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>Reg 0xAA: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8714,25 +9574,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>Reg 0xAB: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8762,25 +9627,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
         <is>
           <t>Reg 0xAC: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8810,25 +9680,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:40</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
         <is>
           <t>Reg 0xAD: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8858,25 +9733,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:06</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>Reg 0xAE: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8906,25 +9786,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>Reg 0xAF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -8954,25 +9839,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>Reg 0xB0: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9002,25 +9892,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
         <is>
           <t>Reg 0xB1: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9050,25 +9945,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>Reg 0xB2: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9098,25 +9998,30 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
         <is>
           <t>Reg 0xB3: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9146,25 +10051,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
         <is>
           <t>Reg 0xB4: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9194,25 +10104,30 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
         <is>
           <t>Reg 0xB5: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9242,25 +10157,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
         <is>
           <t>Reg 0xB6: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9290,25 +10210,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
         <is>
           <t>Reg 0xB7: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9338,25 +10263,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:07</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:41</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
         <is>
           <t>Reg 0xB8: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9386,25 +10316,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
         <is>
           <t>Reg 0xB9: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9434,25 +10369,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
         <is>
           <t>Reg 0xBA: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9482,25 +10422,30 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
         <is>
           <t>Reg 0xBB: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9530,25 +10475,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
         <is>
           <t>Reg 0xBC: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9578,25 +10528,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
         <is>
           <t>Reg 0xBD: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9626,25 +10581,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
         <is>
           <t>Reg 0xBE: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9674,25 +10634,30 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
         <is>
           <t>Reg 0xBF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9722,25 +10687,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
         <is>
           <t>Reg 0xC0: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9770,25 +10740,30 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
         <is>
           <t>Reg 0xC1: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9818,25 +10793,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:42</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
         <is>
           <t>Reg 0xC2: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9866,25 +10846,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:08</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
         <is>
           <t>Reg 0xC3: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9914,25 +10899,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
         <is>
           <t>Reg 0xC4: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -9962,25 +10952,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
         <is>
           <t>Reg 0xC5: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10010,25 +11005,30 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
         <is>
           <t>Reg 0xC6: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10058,25 +11058,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
         <is>
           <t>Reg 0xC7: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10106,25 +11111,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
         <is>
           <t>Reg 0xC8: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10154,25 +11164,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
         <is>
           <t>Reg 0xC9: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10202,25 +11217,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
         <is>
           <t>Reg 0xCA: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10250,25 +11270,30 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
         <is>
           <t>Reg 0xCB: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10298,25 +11323,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:43</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
         <is>
           <t>Reg 0xCC: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10346,25 +11376,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
         <is>
           <t>Reg 0xCD: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10394,25 +11429,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:09</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
         <is>
           <t>Reg 0xCE: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10442,25 +11482,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
         <is>
           <t>Reg 0xCF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10490,25 +11535,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
         <is>
           <t>Reg 0xD0: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10538,25 +11588,30 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
         <is>
           <t>Reg 0xD1: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10586,25 +11641,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
         <is>
           <t>Reg 0xD2: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10634,25 +11694,30 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
         <is>
           <t>Reg 0xD3: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10682,25 +11747,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
         <is>
           <t>Reg 0xD4: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10730,25 +11800,30 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
         <is>
           <t>Reg 0xD5: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10778,25 +11853,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
         <is>
           <t>Reg 0xD6: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10826,25 +11906,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:44</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
         <is>
           <t>Reg 0xD7: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10874,25 +11959,30 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
         <is>
           <t>Reg 0xD8: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10922,25 +12012,30 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:10</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
         <is>
           <t>Reg 0xD9: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -10970,25 +12065,30 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
         <is>
           <t>Reg 0xDA: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11018,25 +12118,30 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
         <is>
           <t>Reg 0xDB: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11066,25 +12171,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
         <is>
           <t>Reg 0xDC: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11114,25 +12224,30 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
         <is>
           <t>Reg 0xDD: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11162,25 +12277,30 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>Reg 0xDE: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11210,25 +12330,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
         <is>
           <t>Reg 0xDF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11258,25 +12383,30 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
         <is>
           <t>Reg 0xE0: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11306,25 +12436,30 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
         <is>
           <t>Reg 0xE1: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11354,25 +12489,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:45</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
         <is>
           <t>Reg 0xE2: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11402,25 +12542,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:11</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
         <is>
           <t>Reg 0xE3: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11450,25 +12595,30 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
         <is>
           <t>Reg 0xE4: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11498,25 +12648,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
         <is>
           <t>Reg 0xE5: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11546,25 +12701,30 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
         <is>
           <t>Reg 0xE6: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11594,25 +12754,30 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
         <is>
           <t>Reg 0xE7: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11642,25 +12807,30 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
         <is>
           <t>Reg 0xE8: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11690,25 +12860,30 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
         <is>
           <t>Reg 0xE9: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11738,25 +12913,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
         <is>
           <t>Reg 0xEA: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11786,25 +12966,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
         <is>
           <t>Reg 0xEB: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11834,25 +13019,30 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:46</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
         <is>
           <t>Reg 0xEC: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11882,25 +13072,30 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
         <is>
           <t>Reg 0xED: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11930,25 +13125,30 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:12</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
         <is>
           <t>Reg 0xEE: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -11978,25 +13178,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
         <is>
           <t>Reg 0xEF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12026,25 +13231,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
         <is>
           <t>Reg 0xF0: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12074,25 +13284,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
         <is>
           <t>Reg 0xF1: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12122,25 +13337,30 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
         <is>
           <t>Reg 0xF2: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12170,25 +13390,30 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
         <is>
           <t>Reg 0xF3: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12218,25 +13443,30 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
         <is>
           <t>Reg 0xF4: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12266,25 +13496,30 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
         <is>
           <t>Reg 0xF5: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12314,25 +13549,30 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
         <is>
           <t>Reg 0xF6: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12362,25 +13602,30 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:13</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:47</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
         <is>
           <t>Reg 0xF7: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12410,25 +13655,30 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
         <is>
           <t>Reg 0xF8: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12458,25 +13708,30 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
         <is>
           <t>Reg 0xF9: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12506,25 +13761,30 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
         <is>
           <t>Reg 0xFA: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12554,25 +13814,30 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
         <is>
           <t>Reg 0xFB: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12602,25 +13867,30 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
         <is>
           <t>Reg 0xFC: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12650,25 +13920,30 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
         <is>
           <t>Reg 0xFD: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12698,25 +13973,30 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
         <is>
           <t>Reg 0xFE: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>
@@ -12746,25 +14026,30 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Rishi</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026-03-11 15:05:14</t>
+          <t>Rishi</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>FullScan</t>
+          <t>2026-03-11 15:23:48</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
+        <is>
+          <t>FullScan</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
         <is>
           <t>Reg 0xFF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
         </is>

--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -8,7 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FullScan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_9_5_Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FullScan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReqCoverage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSA_Extensions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section10_Alarms" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,6 +432,1346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DeviceType</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x01</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CW ITLA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CW ITLA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:38</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DeviceType   (Reg 0x01): len=8 (expected 8) [PASS]  CE=0, STATUS=0 (OK)  STR='CW ITLA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x02</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pilot Photonics</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pilot Photonics</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:39</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Manufacturer (Reg 0x02): len=16 (expected 16) [PASS]  CE=0, STATUS=0 (OK)  STR='Pilot Photonics'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x03</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NYITLA-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NYITLA-01</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:40</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Model        (Reg 0x03): len=10 (expected 10) [PASS]  CE=0, STATUS=0 (OK)  STR='NYITLA-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SerialNumber</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x04</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PP-000123</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PP-000123</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:40</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SerialNumber (Reg 0x04): len=10 (expected 10) [PASS]  CE=0, STATUS=0 (OK)  STR='PP-000123'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MfgDate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x05</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:41</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>MfgDate      (Reg 0x05): len=11 (expected 11) [PASS]  CE=0, STATUS=0 (OK)  STR='2025-08-27'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x06</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:42</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Release      (Reg 0x06): len=6 (expected 6) [PASS]  CE=0, STATUS=0 (OK)  STR='1.0.0'</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RelBack</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x07</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:42</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TableA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>RelBack      (Reg 0x07): len=6 (expected 6) [PASS]  CE=0, STATUS=0 (OK)  STR='1.0.0'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DLConfig</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x14</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DLConfig: REG=0x14, mode=RW, W=0x0001, R=0x0001, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=DLConfig[START], Rdec=DLConfig[START]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:42</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DLStatus</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DLStatus: REG=0x15, mode=RO, OUT=0x0000, CE=0, STATUS=0 (OK), decode=DLStatus[none]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:43</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>StatusF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>StatusF: REG=0x20, mode=RO, OUT=0xD080, CE=0, STATUS=0 (OK), decode=StatusF[XEL,DIS,ALM,SRQ]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:43</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>StatusW</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>StatusW: REG=0x21, mode=RO, OUT=0xD585, CE=0, STATUS=0 (OK), decode=StatusW[LWPWR,LWFREQ,XEL,WPWR,WFREQ,DIS,ALM,SRQ]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:43</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FPowTh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FPowTh: REG=0x22, mode=RW, W=0x0011, R=0x0011, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=0.17 dB, Rdec=0.17 dB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:43</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WPowTh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WPowTh: REG=0x23, mode=RW, W=0x0012, R=0x0012, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=0.18 dB, Rdec=0.18 dB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:43</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FFreqTh</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FFreqTh: REG=0x24, mode=RW, W=0x0013, R=0x0013, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=1.9 GHz coarse, Rdec=1.9 GHz coarse</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:44</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WFreqTh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WFreqTh: REG=0x25, mode=RW, W=0x0014, R=0x0014, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=2.0 GHz coarse, Rdec=2.0 GHz coarse</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:44</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FFreqTh2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x63</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FFreqTh2: REG=0x63, mode=RW, W=0x0017, R=0x0017, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=23 MHz fine, Rdec=23 MHz fine</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:45</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WFreqTh2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x64</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WFreqTh2: REG=0x64, mode=RW, W=0x0018, R=0x0018, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=24 MHz fine, Rdec=24 MHz fine</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:45</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FThermTh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FThermTh: REG=0x26, mode=RW, W=0x0015, R=0x0015, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=0.21 C threshold, Rdec=0.21 C threshold</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:45</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WThermTh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WThermTh: REG=0x27, mode=RW, W=0x0016, R=0x0016, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0000, Wdec=0.22 C threshold, Rdec=0.22 C threshold</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:46</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SRQ_Triggers</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SRQ_Triggers: REG=0x28, mode=RW, W=0x0001, R=0x0001, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x1FBF, Wdec=SRQT[LFPWR], Rdec=SRQT[LFPWR]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:46</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FatalTriggers</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FatalTriggers: REG=0x29, mode=RW, W=0x0001, R=0x0001, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x000F, Wdec=FatalT[LFPWR], Rdec=FatalT[LFPWR]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:46</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALMT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ALMT: REG=0x2A, mode=RW, W=0x0001, R=0x0001, CEw=0, STw=0 (OK), CEr=0, STr=0 (OK), orig=0x0D0D, Wdec=ALMT[FPWR], Rdec=ALMT[FPWR]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:55:47</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Table9.5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -526,7 +1871,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:24</t>
+          <t>2026-03-11 16:55:47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -536,7 +1881,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Reg 0x00: OUT=0x8001, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x00: OUT=0x8000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -579,7 +1924,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:24</t>
+          <t>2026-03-11 16:55:47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,7 +1977,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:24</t>
+          <t>2026-03-11 16:55:47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -685,7 +2030,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:24</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -738,7 +2083,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -791,7 +2136,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -844,7 +2189,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,7 +2242,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -950,7 +2295,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1003,7 +2348,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1013,7 +2358,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Reg 0x09: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x09: OUT=0x0001, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -1056,7 +2401,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1109,7 +2454,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1147,12 +2492,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1162,7 +2507,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1215,7 +2560,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:25</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1268,7 +2613,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1321,7 +2666,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1374,7 +2719,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1412,12 +2757,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1427,7 +2772,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1465,12 +2810,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Not Implemented</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1480,7 +2825,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1533,7 +2878,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1586,7 +2931,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1639,7 +2984,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1692,7 +3037,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1745,7 +3090,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:49</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1798,7 +3143,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:26</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1851,7 +3196,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1904,7 +3249,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1957,7 +3302,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2010,7 +3355,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2063,7 +3408,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2116,7 +3461,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2169,7 +3514,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2222,7 +3567,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2275,7 +3620,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2328,7 +3673,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2381,7 +3726,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:27</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2434,7 +3779,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2487,7 +3832,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2540,7 +3885,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2593,7 +3938,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2646,7 +3991,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2699,7 +4044,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2752,7 +4097,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2805,7 +4150,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2858,7 +4203,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:51</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2911,7 +4256,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:28</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2964,7 +4309,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3017,7 +4362,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3070,7 +4415,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3123,7 +4468,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3176,7 +4521,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3229,7 +4574,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3282,7 +4627,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3335,7 +4680,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3388,7 +4733,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3441,7 +4786,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:52</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3494,7 +4839,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:29</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3547,7 +4892,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3600,7 +4945,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3653,7 +4998,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3706,7 +5051,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3759,7 +5104,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3812,7 +5157,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3865,7 +5210,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3918,7 +5263,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3971,7 +5316,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4024,7 +5369,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:53</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4077,7 +5422,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:30</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4130,7 +5475,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4183,7 +5528,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4236,7 +5581,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4289,7 +5634,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4342,7 +5687,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4395,7 +5740,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4448,7 +5793,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4501,7 +5846,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4554,7 +5899,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4607,7 +5952,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:31</t>
+          <t>2026-03-11 16:55:54</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4660,7 +6005,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4713,7 +6058,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4766,7 +6111,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4819,7 +6164,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4872,7 +6217,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4925,7 +6270,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4978,7 +6323,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5031,7 +6376,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5084,7 +6429,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5137,7 +6482,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:55</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5190,7 +6535,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:32</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5243,7 +6588,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5296,7 +6641,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5349,7 +6694,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5402,7 +6747,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5455,7 +6800,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5508,7 +6853,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5561,7 +6906,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5614,7 +6959,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5667,7 +7012,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:56</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5720,7 +7065,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5773,7 +7118,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:33</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5826,7 +7171,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5879,7 +7224,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5932,7 +7277,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5985,7 +7330,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6038,7 +7383,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6091,7 +7436,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6144,7 +7489,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6197,7 +7542,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6250,7 +7595,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:57</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6303,7 +7648,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:34</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6356,7 +7701,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6409,7 +7754,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6462,7 +7807,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6515,7 +7860,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6568,7 +7913,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6621,7 +7966,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6674,7 +8019,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6727,7 +8072,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6780,7 +8125,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6833,7 +8178,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:58</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6886,7 +8231,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:35</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6939,7 +8284,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6992,7 +8337,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7045,7 +8390,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7098,7 +8443,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7151,7 +8496,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7204,7 +8549,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7257,7 +8602,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7310,7 +8655,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7363,7 +8708,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7416,7 +8761,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:36</t>
+          <t>2026-03-11 16:55:59</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7469,7 +8814,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7522,7 +8867,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7575,7 +8920,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7628,7 +8973,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7681,7 +9026,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7734,7 +9079,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7787,7 +9132,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7840,7 +9185,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7850,7 +9195,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Reg 0x8A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8A: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7893,7 +9238,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7903,7 +9248,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Reg 0x8B: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8B: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7946,7 +9291,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7999,7 +9344,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:37</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8052,7 +9397,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8105,7 +9450,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8158,7 +9503,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8211,7 +9556,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8264,7 +9609,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8317,7 +9662,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8370,7 +9715,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8423,7 +9768,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8476,7 +9821,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:01</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8529,7 +9874,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8582,7 +9927,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:38</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8635,7 +9980,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8688,7 +10033,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8741,7 +10086,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8794,7 +10139,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8847,7 +10192,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -8900,7 +10245,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -8953,7 +10298,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9006,7 +10351,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9059,7 +10404,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:02</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9112,7 +10457,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:39</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9165,7 +10510,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9218,7 +10563,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9271,7 +10616,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9324,7 +10669,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9377,7 +10722,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9430,7 +10775,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9483,7 +10828,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9536,7 +10881,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9589,7 +10934,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9642,7 +10987,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:03</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9695,7 +11040,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:40</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -9748,7 +11093,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -9801,7 +11146,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -9854,7 +11199,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -9907,7 +11252,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -9960,7 +11305,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10013,7 +11358,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10066,7 +11411,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10119,7 +11464,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10172,7 +11517,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:04</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10225,7 +11570,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10278,7 +11623,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:41</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10331,7 +11676,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -10384,7 +11729,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10437,7 +11782,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10490,7 +11835,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10543,7 +11888,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10596,7 +11941,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10649,7 +11994,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -10702,7 +12047,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -10755,7 +12100,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:05</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10808,7 +12153,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:42</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -10861,7 +12206,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -10914,7 +12259,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -10967,7 +12312,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11020,7 +12365,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11073,7 +12418,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11126,7 +12471,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11179,7 +12524,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11232,7 +12577,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11285,7 +12630,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:06</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11338,7 +12683,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:43</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -11391,7 +12736,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11444,7 +12789,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11497,7 +12842,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -11550,7 +12895,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -11603,7 +12948,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -11656,7 +13001,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -11709,7 +13054,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11762,7 +13107,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -11815,7 +13160,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:07</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -11868,7 +13213,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -11921,7 +13266,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:44</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -11974,7 +13319,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12027,7 +13372,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12080,7 +13425,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12133,7 +13478,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12186,7 +13531,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -12239,7 +13584,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -12292,7 +13637,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -12345,7 +13690,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -12398,7 +13743,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:08</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -12451,7 +13796,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -12504,7 +13849,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:45</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -12557,7 +13902,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -12610,7 +13955,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -12663,7 +14008,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -12716,7 +14061,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -12769,7 +14114,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -12822,7 +14167,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -12875,7 +14220,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -12928,7 +14273,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:09</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -12981,7 +14326,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13034,7 +14379,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:46</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13087,7 +14432,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13140,7 +14485,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -13193,7 +14538,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -13246,7 +14591,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -13299,7 +14644,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13352,7 +14697,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -13405,7 +14750,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -13458,7 +14803,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -13511,7 +14856,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:10</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -13564,7 +14909,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -13617,7 +14962,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:47</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -13670,7 +15015,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13723,7 +15068,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -13776,7 +15121,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -13829,7 +15174,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -13882,7 +15227,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -13935,7 +15280,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -13988,7 +15333,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -14041,7 +15386,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-03-11 15:23:48</t>
+          <t>2026-03-11 16:56:11</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -14052,6 +15397,838 @@
       <c r="K257" t="inlineStr">
         <is>
           <t>Reg 0xFF: OUT=0x0000, CE=0, STATUS=1 (XE)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Module status / alarms / triggers</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:12</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>General module configuration</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:13</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fine tune / limits</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:14</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Health / dither / age</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Manufacturer specific (implemented subset)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:16</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tuners</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ERROR: name 'write_tuners' is not defined</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:18</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MSA_Extensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ERROR: name 'write_soa' is not defined</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MSA_Extensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bias</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ERROR: name 'write_bias' is not defined</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:18</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MSA_Extensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TEC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ERROR: name 'write_tec' is not defined</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MSA_Extensions</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SRQ_Triggers</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>W=0x0003 R=0x0003 orig=0x1FBF CEw=0 STw=0 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:19</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FatalTriggers</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>W=0x000F R=0x000F orig=0x000F CEw=0 STw=0 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:19</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ALM_Triggers</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>W=0x0007 R=0x0007 orig=0x0D0D CEw=0 STw=0 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>StatusF_COW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Read1=0xD080(CE=0,ST=0) Read2=0xD080(CE=0,ST=0) COW_cleared=No (live alarms present)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>StatusW_COW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Read1=0xD585(CE=0,ST=0) Read2=0xD585(CE=0,ST=0) COW_cleared=No (live alarms present)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MCB_ADT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x33</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MCB ADT: set=0x0003(bit 1) clr=0x0002(bit 0)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MCB_SDF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x33</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MCB SDF: set=0x0002(bit 1) clr=0x0000(bit 0)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:56:21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Section10_Alarms</t>
         </is>
       </c>
     </row>

--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:38</t>
+          <t>2026-03-11 17:37:20</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:39</t>
+          <t>2026-03-11 17:37:21</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:40</t>
+          <t>2026-03-11 17:37:22</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:40</t>
+          <t>2026-03-11 17:37:22</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:41</t>
+          <t>2026-03-11 17:37:23</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:42</t>
+          <t>2026-03-11 17:37:24</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:42</t>
+          <t>2026-03-11 17:37:24</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:42</t>
+          <t>2026-03-11 17:37:24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:43</t>
+          <t>2026-03-11 17:37:25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:43</t>
+          <t>2026-03-11 17:37:25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:43</t>
+          <t>2026-03-11 17:37:25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:43</t>
+          <t>2026-03-11 17:37:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:43</t>
+          <t>2026-03-11 17:37:25</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:44</t>
+          <t>2026-03-11 17:37:26</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:44</t>
+          <t>2026-03-11 17:37:26</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:45</t>
+          <t>2026-03-11 17:37:27</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:45</t>
+          <t>2026-03-11 17:37:27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:45</t>
+          <t>2026-03-11 17:37:27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:46</t>
+          <t>2026-03-11 17:37:28</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:46</t>
+          <t>2026-03-11 17:37:28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:46</t>
+          <t>2026-03-11 17:37:28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:47</t>
+          <t>2026-03-11 17:37:29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:47</t>
+          <t>2026-03-11 17:37:29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:47</t>
+          <t>2026-03-11 17:37:29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:47</t>
+          <t>2026-03-11 17:37:29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:48</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:49</t>
+          <t>2026-03-11 17:37:31</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:50</t>
+          <t>2026-03-11 17:37:32</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:51</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:33</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:52</t>
+          <t>2026-03-11 17:37:34</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:53</t>
+          <t>2026-03-11 17:37:35</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:36</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:54</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:55</t>
+          <t>2026-03-11 17:37:37</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:56</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:38</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:57</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:39</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:58</t>
+          <t>2026-03-11 17:37:40</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:41</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-11 16:55:59</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Reg 0x8A: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Reg 0x8B: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8B: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:00</t>
+          <t>2026-03-11 17:37:42</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:01</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:43</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:02</t>
+          <t>2026-03-11 17:37:44</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:03</t>
+          <t>2026-03-11 17:37:45</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:04</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:46</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:47</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:05</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:06</t>
+          <t>2026-03-11 17:37:48</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:07</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:49</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:08</t>
+          <t>2026-03-11 17:37:50</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:09</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:51</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:10</t>
+          <t>2026-03-11 17:37:52</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:11</t>
+          <t>2026-03-11 17:37:53</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:12</t>
+          <t>2026-03-11 17:37:54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:13</t>
+          <t>2026-03-11 17:37:55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:14</t>
+          <t>2026-03-11 17:37:56</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:15</t>
+          <t>2026-03-11 17:37:57</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:16</t>
+          <t>2026-03-11 17:37:58</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ERROR: name 'write_tuners' is not defined</t>
+          <t>Wrote phase=12.12,ring1=9.99,ring2=5.55 | Read phase=12.120,ring1=9.990,ring2=5.550</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:18</t>
+          <t>2026-03-11 17:38:01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -15752,12 +15752,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERROR: name 'write_soa' is not defined</t>
+          <t>Wrote soa=1.23 | Read soa=1.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:18</t>
+          <t>2026-03-11 17:38:01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -15784,12 +15784,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERROR: name 'write_bias' is not defined</t>
+          <t>Wrote bias=123 | Read bias=123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:18</t>
+          <t>2026-03-11 17:38:01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERROR: name 'write_tec' is not defined</t>
+          <t>Wrote tec=-45 | Read tec=-45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:18</t>
+          <t>2026-03-11 17:38:02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:19</t>
+          <t>2026-03-11 17:38:02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:19</t>
+          <t>2026-03-11 17:38:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:20</t>
+          <t>2026-03-11 17:38:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:20</t>
+          <t>2026-03-11 17:38:03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:20</t>
+          <t>2026-03-11 17:38:04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:20</t>
+          <t>2026-03-11 17:38:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11 16:56:21</t>
+          <t>2026-03-11 17:38:04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">

--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -14,6 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReqCoverage" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSA_Extensions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section10_Alarms" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section9_6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section9_7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section9_8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section9_9" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,6 +430,1500 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Currents</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x57</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Currents: REG=0x57 mode=RO OUT=0x0008 CE=0 STATUS=0 (OK) [Currents[TEC=-4.5mA, DIODE=12.3mA, MON=0.0mA, SOA=1.2mA]]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:27</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Temps</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x58</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Temps: REG=0x58 mode=RO OUT=0x0004 CE=0 STATUS=0 (OK) [Temps[DIODE=25.00C, CASE=-45.00C]]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CaseTemp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CaseTemp: REG=0x59 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK) [0.00 C]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:28</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DitherPer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x5A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DitherPer: REG=0x5A mode=RO OUT=0x0064 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DitherBW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x5B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DitherBW: REG=0x5B mode=RO OUT=0x0000 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DevCap</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DevCap: REG=0x5C mode=RO OUT=0x0000 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DevCap2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DevCap2: REG=0x5D mode=RO OUT=0xFE0C CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DevCap3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x5E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DevCap3: REG=0x5E mode=RO OUT=0x1B58 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DevCap4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DevCap4: REG=0x5F mode=RO OUT=0x0000 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rsvd_60</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rsvd_60: REG=0x60 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FTFMin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FTFMin: REG=0x61 mode=RO OUT=0x0001 CE=0 STATUS=0 (OK) [1 MHz]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FTF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FTF: REG=0x62 mode=RW W=0x0000 R=0x0000 CEw=0 STw=0 CEr=0 STr=0 [0 MHz]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:29</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Section9.8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x80</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>V1: REG=0x80 mode=RO OUT=0x2706 CE=0 STATUS=0 (OK) [99.900]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x81</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>V2: REG=0x81 mode=RO OUT=0x15AE CE=0 STATUS=0 (OK) [55.500]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x82</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>V3: REG=0x82 mode=RO OUT=0x2F58 CE=0 STATUS=0 (OK) [121.200]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x83</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gain: REG=0x83 mode=RO OUT=0x007B CE=0 STATUS=0 (OK) [1.230]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SOA_tel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x84</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SOA_tel: REG=0x84 mode=RO OUT=0x007B CE=0 STATUS=0 (OK) [1.230]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Temp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x85</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Temp: REG=0x85 mode=RO OUT=0xFE3E CE=0 STATUS=0 (OK) [-45.0 C]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MPD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x86</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MPD: REG=0x86 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK) [0.00 (PD)]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WLPD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x87</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WLPD: REG=0x87 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK) [0.00 (PD)]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WMPD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x88</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WMPD: REG=0x88 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK) [0.00 (PD)]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WL_PD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x89</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WL_PD: REG=0x89 mode=RO OUT=0x000A CE=0 STATUS=0 (OK) [1.00 (PD)]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Etalon_PD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x8A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Etalon_PD: REG=0x8A mode=RO OUT=0x000A CE=0 STATUS=0 (OK) [1.00 (PD)]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:31</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Power_PD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x8B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Power_PD: REG=0x8B mode=RO OUT=0x000A CE=0 STATUS=0 (OK) [1.00 (PD)]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:31</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TunerPhase</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x8C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TunerPhase: REG=0x8C mode=RW W=0x2F58 R=0x2F58 CEw=0 STw=0 CEr=0 STr=0 [12.1200]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:31</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TunerRing1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x8D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TunerRing1: REG=0x8D mode=RW W=0x2706 R=0x2706 CEw=0 STw=0 CEr=0 STr=0 [9.9900]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:31</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TunerRing2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8E</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TunerRing2: REG=0x8E mode=RW W=0x15AE R=0x15AE CEw=0 STw=0 CEr=0 STr=0 [5.5500]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:32</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x8F</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SOA: REG=0x8F mode=RW W=0x007B R=0x007B CEw=0 STw=0 CEr=0 STr=0 [1.230]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:32</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bias</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bias: REG=0x90 mode=RW W=0x007B R=0x007B CEw=0 STw=0 CEr=0 STr=0 [123]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:32</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TEC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TEC: REG=0x91 mode=RW W=0xFFD3 R=0xFFD3 CEw=0 STw=0 CEr=0 STr=0 [-45]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:33</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rsvd_92</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x92</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rsvd_92: REG=0x92 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:33</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Section9.9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -577,7 +2075,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:20</t>
+          <t>2026-03-11 17:55:37</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -651,7 +2149,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:21</t>
+          <t>2026-03-11 17:55:38</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -725,7 +2223,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:22</t>
+          <t>2026-03-11 17:55:39</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -799,7 +2297,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:22</t>
+          <t>2026-03-11 17:55:40</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -873,7 +2371,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:23</t>
+          <t>2026-03-11 17:55:41</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -947,7 +2445,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:24</t>
+          <t>2026-03-11 17:55:41</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1021,7 +2519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:24</t>
+          <t>2026-03-11 17:55:42</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1164,7 +2662,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:24</t>
+          <t>2026-03-11 17:55:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1206,7 +2704,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:25</t>
+          <t>2026-03-11 17:55:42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1248,7 +2746,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:25</t>
+          <t>2026-03-11 17:55:42</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1290,7 +2788,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:25</t>
+          <t>2026-03-11 17:55:42</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1332,7 +2830,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:25</t>
+          <t>2026-03-11 17:55:42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1374,7 +2872,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:25</t>
+          <t>2026-03-11 17:55:43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1416,7 +2914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:26</t>
+          <t>2026-03-11 17:55:43</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,7 +2956,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:26</t>
+          <t>2026-03-11 17:55:44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1500,7 +2998,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:27</t>
+          <t>2026-03-11 17:55:44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1542,7 +3040,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:27</t>
+          <t>2026-03-11 17:55:44</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1584,7 +3082,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:27</t>
+          <t>2026-03-11 17:55:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1626,7 +3124,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:28</t>
+          <t>2026-03-11 17:55:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1668,7 +3166,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:28</t>
+          <t>2026-03-11 17:55:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1710,7 +3208,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:28</t>
+          <t>2026-03-11 17:55:46</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1752,7 +3250,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:29</t>
+          <t>2026-03-11 17:55:46</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1871,7 +3369,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:29</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1924,7 +3422,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:29</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1977,7 +3475,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:29</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2030,7 +3528,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2083,7 +3581,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2136,7 +3634,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2189,7 +3687,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2242,7 +3740,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2295,7 +3793,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2348,7 +3846,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2401,7 +3899,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2454,7 +3952,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2507,7 +4005,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2560,7 +4058,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:30</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2613,7 +4111,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2666,7 +4164,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2719,7 +4217,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2772,7 +4270,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2825,7 +4323,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2878,7 +4376,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:48</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2931,7 +4429,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2984,7 +4482,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3037,7 +4535,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3090,7 +4588,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:31</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3143,7 +4641,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3196,7 +4694,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3249,7 +4747,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3302,7 +4800,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3355,7 +4853,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3408,7 +4906,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3461,7 +4959,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:49</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3514,7 +5012,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3567,7 +5065,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3620,7 +5118,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3673,7 +5171,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:32</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3726,7 +5224,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3779,7 +5277,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3832,7 +5330,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3885,7 +5383,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3938,7 +5436,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3991,7 +5489,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4044,7 +5542,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:50</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4097,7 +5595,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4150,7 +5648,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4203,7 +5701,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4256,7 +5754,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:33</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4309,7 +5807,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4362,7 +5860,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4415,7 +5913,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4468,7 +5966,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4521,7 +6019,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4574,7 +6072,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:51</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4627,7 +6125,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4680,7 +6178,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4733,7 +6231,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4786,7 +6284,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:34</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4839,7 +6337,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4892,7 +6390,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4945,7 +6443,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4998,7 +6496,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5051,7 +6549,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5104,7 +6602,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5157,7 +6655,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:52</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5210,7 +6708,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5263,7 +6761,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5316,7 +6814,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5369,7 +6867,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:35</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5422,7 +6920,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5475,7 +6973,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5528,7 +7026,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5581,7 +7079,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5634,7 +7132,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5687,7 +7185,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:53</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5740,7 +7238,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5793,7 +7291,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5846,7 +7344,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5899,7 +7397,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:36</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5952,7 +7450,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6005,7 +7503,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6058,7 +7556,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6111,7 +7609,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6164,7 +7662,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6217,7 +7715,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6270,7 +7768,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:54</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6323,7 +7821,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6376,7 +7874,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6429,7 +7927,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6482,7 +7980,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:37</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6535,7 +8033,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6588,7 +8086,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6641,7 +8139,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6694,7 +8192,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6747,7 +8245,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6800,7 +8298,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:55</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6853,7 +8351,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6906,7 +8404,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6959,7 +8457,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -7012,7 +8510,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -7022,7 +8520,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Reg 0x61: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x61: OUT=0x0001, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -7065,7 +8563,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:38</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -7118,7 +8616,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7171,7 +8669,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7224,7 +8722,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7277,7 +8775,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7330,7 +8828,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7383,7 +8881,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:56</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7436,7 +8934,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7489,7 +8987,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7542,7 +9040,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7595,7 +9093,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7648,7 +9146,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:39</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7701,7 +9199,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7754,7 +9252,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7807,7 +9305,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7860,7 +9358,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7913,7 +9411,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7966,7 +9464,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:57</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -8019,7 +9517,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8072,7 +9570,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8125,7 +9623,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8178,7 +9676,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:40</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8231,7 +9729,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8284,7 +9782,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8337,7 +9835,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8390,7 +9888,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8443,7 +9941,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8496,7 +9994,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:58</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8549,7 +10047,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8602,7 +10100,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8655,7 +10153,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8665,7 +10163,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Reg 0x80: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x80: OUT=0x2706, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8708,7 +10206,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:41</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8718,7 +10216,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Reg 0x81: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x81: OUT=0x15AE, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8761,7 +10259,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8771,7 +10269,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Reg 0x82: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x82: OUT=0x2F58, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8814,7 +10312,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8824,7 +10322,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Reg 0x83: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x83: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8867,7 +10365,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8877,7 +10375,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Reg 0x84: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x84: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8920,7 +10418,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8930,7 +10428,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Reg 0x85: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x85: OUT=0xFE3E, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8973,7 +10471,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9026,7 +10524,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:55:59</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9079,7 +10577,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9132,7 +10630,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9185,7 +10683,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9195,7 +10693,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Reg 0x8A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8A: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9238,7 +10736,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +10789,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:42</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9301,7 +10799,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Reg 0x8C: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8C: OUT=0x2F58, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9344,7 +10842,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9354,7 +10852,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Reg 0x8D: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8D: OUT=0x2706, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9397,7 +10895,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9407,7 +10905,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Reg 0x8E: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8E: OUT=0x15AE, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9450,7 +10948,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9460,7 +10958,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Reg 0x8F: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8F: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9503,7 +11001,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9513,7 +11011,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Reg 0x90: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x90: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9556,7 +11054,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9566,7 +11064,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Reg 0x91: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x91: OUT=0xFFD3, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -9609,7 +11107,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9662,7 +11160,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9715,7 +11213,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9768,7 +11266,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9821,7 +11319,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9874,7 +11372,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:43</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9927,7 +11425,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9980,7 +11478,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10033,7 +11531,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10086,7 +11584,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10139,7 +11637,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10192,7 +11690,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:01</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10245,7 +11743,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10298,7 +11796,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10351,7 +11849,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10404,7 +11902,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:44</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10457,7 +11955,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10510,7 +12008,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10563,7 +12061,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10616,7 +12114,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10669,7 +12167,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10722,7 +12220,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10775,7 +12273,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:02</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10828,7 +12326,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10881,7 +12379,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10934,7 +12432,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10987,7 +12485,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:45</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11040,7 +12538,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11093,7 +12591,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11146,7 +12644,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11199,7 +12697,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11252,7 +12750,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11305,7 +12803,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:03</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11358,7 +12856,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11411,7 +12909,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11464,7 +12962,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11517,7 +13015,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11570,7 +13068,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:46</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11623,7 +13121,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11676,7 +13174,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11729,7 +13227,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11782,7 +13280,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11835,7 +13333,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11888,7 +13386,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:04</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11941,7 +13439,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11994,7 +13492,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12047,7 +13545,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:47</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12100,7 +13598,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12153,7 +13651,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12206,7 +13704,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12259,7 +13757,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12312,7 +13810,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12365,7 +13863,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12418,7 +13916,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:05</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12471,7 +13969,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12524,7 +14022,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12577,7 +14075,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12630,7 +14128,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:48</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12683,7 +14181,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12736,7 +14234,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12789,7 +14287,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12842,7 +14340,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12895,7 +14393,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12948,7 +14446,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:06</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13001,7 +14499,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13054,7 +14552,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13107,7 +14605,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13160,7 +14658,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13213,7 +14711,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:49</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13266,7 +14764,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13319,7 +14817,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13372,7 +14870,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13425,7 +14923,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13478,7 +14976,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13531,7 +15029,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:07</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13584,7 +15082,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13637,7 +15135,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13690,7 +15188,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13743,7 +15241,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:50</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13796,7 +15294,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13849,7 +15347,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13902,7 +15400,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13955,7 +15453,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14008,7 +15506,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14061,7 +15559,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:08</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -14114,7 +15612,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14167,7 +15665,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14220,7 +15718,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14273,7 +15771,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14326,7 +15824,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:51</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14379,7 +15877,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14432,7 +15930,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14485,7 +15983,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14538,7 +16036,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14591,7 +16089,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:09</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14644,7 +16142,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14697,7 +16195,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14750,7 +16248,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14803,7 +16301,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14856,7 +16354,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:52</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14909,7 +16407,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14962,7 +16460,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -15015,7 +16513,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15068,7 +16566,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15121,7 +16619,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15174,7 +16672,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:10</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -15227,7 +16725,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:11</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -15280,7 +16778,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:11</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -15333,7 +16831,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:11</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15386,7 +16884,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:53</t>
+          <t>2026-03-11 17:56:11</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -15525,7 +17023,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:54</t>
+          <t>2026-03-11 17:56:11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -15559,7 +17057,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:55</t>
+          <t>2026-03-11 17:56:12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -15593,7 +17091,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:56</t>
+          <t>2026-03-11 17:56:14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -15627,7 +17125,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:57</t>
+          <t>2026-03-11 17:56:15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -15661,7 +17159,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:37:58</t>
+          <t>2026-03-11 17:56:16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -15735,7 +17233,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:01</t>
+          <t>2026-03-11 17:56:18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -15767,7 +17265,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:01</t>
+          <t>2026-03-11 17:56:19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -15799,7 +17297,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:01</t>
+          <t>2026-03-11 17:56:19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -15831,7 +17329,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:02</t>
+          <t>2026-03-11 17:56:19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -16001,7 +17499,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:02</t>
+          <t>2026-03-11 17:56:19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -16038,7 +17536,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:03</t>
+          <t>2026-03-11 17:56:20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -16075,7 +17573,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:03</t>
+          <t>2026-03-11 17:56:20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -16112,7 +17610,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:03</t>
+          <t>2026-03-11 17:56:20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16149,7 +17647,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:04</t>
+          <t>2026-03-11 17:56:21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -16186,7 +17684,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:04</t>
+          <t>2026-03-11 17:56:21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -16223,12 +17721,1296 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:38:04</t>
+          <t>2026-03-11 17:56:21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Section10_Alarms</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Channel: REG=0x30 mode=RW W=0x0000 R=0x0000 CEw=0 STw=1 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:22</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ChannelH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x65</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ChannelH: REG=0x65 mode=RW W=0x0000 R=0x0000 CEw=0 STw=0 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:22</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Power: REG=0x31 mode=RW W=0x0000 R=0x0000 CEw=0 STw=0 CEr=0 STr=0 [0.00 dBm]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:22</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ResEna</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x32</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ResEna: REG=0x32 mode=RW W=0x0000 R=0x0000 CEw=0 STw=0 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MCB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x33</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MCB: REG=0x33 mode=RW W=0x0002 R=0x0002 CEw=0 STw=0 CEr=0 STr=0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:23</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Grid</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x34</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Grid: REG=0x34 mode=RW W=0x01F4 R=0x01F4 CEw=0 STw=0 CEr=0 STr=0 [50.0 GHz]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:24</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Grid2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x66</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grid2: REG=0x66 mode=RW W=0x0000 R=0x0000 CEw=0 STw=0 CEr=0 STr=0 [0 MHz]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:24</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FCF1_THz</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x35</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FCF1_THz: REG=0x35 mode=RW W=0x00C1 R=0x00C1 CEw=0 STw=0 CEr=0 STr=0 [193 THz]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:24</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF2_G10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FCF2_G10: REG=0x36 mode=RW W=0x1194 R=0x1194 CEw=0 STw=0 CEr=0 STr=0 [450.0 GHz×10]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCF3_MHz</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FCF3_MHz: REG=0x67 mode=RW W=0x0000 R=0x0000 CEw=0 STw=0 CEr=0 STr=0 [0 MHz]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:25</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LF1_THz</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LF1_THz: REG=0x40 mode=RO OUT=0x00C1 CE=0 STATUS=0 (OK) [193 THz]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:25</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LF2_G10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LF2_G10: REG=0x41 mode=RO OUT=0x1194 CE=0 STATUS=0 (OK) [450.0 GHz×10]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:25</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LF3_MHz</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x68</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LF3_MHz: REG=0x68 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LF1Min</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x42</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LF1Min: REG=0x42 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK) [0 THz]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LF1Max</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x43</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LF1Max: REG=0x43 mode=RO OUT=0x09C4 CE=0 STATUS=0 (OK) [2500 THz]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Section9.6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpectedLen</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LenResult</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID_String</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expected_ID_Substr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ID_Result</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>STATUS_Text</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverallResult</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MinFreq_THz</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x4F</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>THz</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MinFreq_THz: REG=0x4F OUT=0x1388 CE=0 STATUS=0 (OK) [5000 THz]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MinFreq_G10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x50</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GHz×10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MinFreq_G10: REG=0x50 OUT=0x0000 CE=0 STATUS=0 (OK) [0.0 GHz]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MaxFreq_THz</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>THz</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MaxFreq_THz: REG=0x51 OUT=0x07D0 CE=0 STATUS=0 (OK) [2000 THz]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MaxFreq_G10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GHz×10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MaxFreq_G10: REG=0x52 OUT=0x00C1 CE=0 STATUS=0 (OK) [19.3 GHz]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MinPower</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dBm×100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MinPower: REG=0x53 OUT=0x1194 CE=0 STATUS=0 (OK) [45.00 dBm]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MaxPower</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dBm×100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MaxPower: REG=0x69 OUT=0x0000 CE=0 STATUS=0 (OK) [0.00 dBm]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:26</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LastF_THz</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x54</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>THz</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LastF_THz: REG=0x54 OUT=0x00C6 CE=0 STATUS=0 (OK) [198 THz]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:27</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LastF_G10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x55</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GHz×10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LastF_G10: REG=0x55 OUT=0x1194 CE=0 STATUS=0 (OK) [450.0 GHz]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:27</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LastF_MHz</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x6A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LastF_MHz: REG=0x6A OUT=0x0000 CE=0 STATUS=0 (OK) [0 MHz]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:27</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LGrid10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x56</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GHz×10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LGrid10: REG=0x56 OUT=0x00FA CE=0 STATUS=0 (OK) [25.0 GHz]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:27</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGrid2_MHz</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LGrid2_MHz: REG=0x6B OUT=0x0000 CE=0 STATUS=0 (OK) [0 MHz]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:56:27</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Section9.7</t>
         </is>
       </c>
     </row>

--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Currents: REG=0x57 mode=RO OUT=0x0008 CE=0 STATUS=0 (OK) [Currents[TEC=-4.5mA, DIODE=12.3mA, MON=0.0mA, SOA=1.2mA]]</t>
+          <t>Currents: REG=0x57 mode=RO OUT=0x0008 CE=0 STATUS=0 (OK) [Currents[TEC=-4.5mA, DIODE=12.3mA, MON=1.0mA, SOA=1.2mA]]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:27</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:28</t>
+          <t>2026-03-12 09:04:51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:28</t>
+          <t>2026-03-12 09:04:51</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:28</t>
+          <t>2026-03-12 09:04:51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:28</t>
+          <t>2026-03-12 09:04:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:29</t>
+          <t>2026-03-12 09:04:52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WL_PD: REG=0x89 mode=RO OUT=0x000A CE=0 STATUS=0 (OK) [1.00 (PD)]</t>
+          <t>WL_PD: REG=0x89 mode=RO OUT=0x0000 CE=0 STATUS=0 (OK) [0.00 (PD)]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:30</t>
+          <t>2026-03-12 09:04:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:31</t>
+          <t>2026-03-12 09:04:54</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:31</t>
+          <t>2026-03-12 09:04:54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:31</t>
+          <t>2026-03-12 09:04:54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:31</t>
+          <t>2026-03-12 09:04:54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:32</t>
+          <t>2026-03-12 09:04:54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:32</t>
+          <t>2026-03-12 09:04:55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:32</t>
+          <t>2026-03-12 09:04:55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:33</t>
+          <t>2026-03-12 09:04:56</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:33</t>
+          <t>2026-03-12 09:04:56</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:37</t>
+          <t>2026-03-12 09:04:01</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:38</t>
+          <t>2026-03-12 09:04:02</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:39</t>
+          <t>2026-03-12 09:04:02</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:40</t>
+          <t>2026-03-12 09:04:03</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:41</t>
+          <t>2026-03-12 09:04:04</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:41</t>
+          <t>2026-03-12 09:04:05</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:42</t>
+          <t>2026-03-12 09:04:05</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:42</t>
+          <t>2026-03-12 09:04:05</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:42</t>
+          <t>2026-03-12 09:04:06</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>StatusF: REG=0x20, mode=RO, OUT=0xD080, CE=0, STATUS=0 (OK), decode=StatusF[XEL,DIS,ALM,SRQ]</t>
+          <t>StatusF: REG=0x20, mode=RO, OUT=0xD000, CE=0, STATUS=0 (OK), decode=StatusF[DIS,ALM,SRQ]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:42</t>
+          <t>2026-03-12 09:04:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>StatusW: REG=0x21, mode=RO, OUT=0xD585, CE=0, STATUS=0 (OK), decode=StatusW[LWPWR,LWFREQ,XEL,WPWR,WFREQ,DIS,ALM,SRQ]</t>
+          <t>StatusW: REG=0x21, mode=RO, OUT=0xD505, CE=0, STATUS=0 (OK), decode=StatusW[LWPWR,LWFREQ,WPWR,WFREQ,DIS,ALM,SRQ]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:42</t>
+          <t>2026-03-12 09:04:06</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:42</t>
+          <t>2026-03-12 09:04:06</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:43</t>
+          <t>2026-03-12 09:04:06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:43</t>
+          <t>2026-03-12 09:04:07</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:44</t>
+          <t>2026-03-12 09:04:07</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:44</t>
+          <t>2026-03-12 09:04:07</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:44</t>
+          <t>2026-03-12 09:04:08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:45</t>
+          <t>2026-03-12 09:04:08</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:45</t>
+          <t>2026-03-12 09:04:08</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:45</t>
+          <t>2026-03-12 09:04:09</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:46</t>
+          <t>2026-03-12 09:04:09</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:46</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:47</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:48</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:49</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:13</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:50</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:51</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:52</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:16</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:53</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:17</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:54</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:18</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:55</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Reg 0x61: OUT=0x0001, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x61: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:19</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:56</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:20</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:57</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:21</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:58</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Reg 0x80: OUT=0x2706, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x80: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Reg 0x81: OUT=0x15AE, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x81: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Reg 0x82: OUT=0x2F58, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x82: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Reg 0x83: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x83: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:22</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Reg 0x84: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x84: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Reg 0x85: OUT=0xFE3E, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x85: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-11 17:55:59</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Reg 0x8A: OUT=0x000A, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8A: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Reg 0x8C: OUT=0x2F58, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8C: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Reg 0x8D: OUT=0x2706, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8D: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Reg 0x8E: OUT=0x15AE, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8E: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:23</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Reg 0x8F: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x8F: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Reg 0x90: OUT=0x007B, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x90: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Reg 0x91: OUT=0xFFD3, CE=0, STATUS=0 (OK)</t>
+          <t>Reg 0x91: OUT=0x0000, CE=0, STATUS=0 (OK)</t>
         </is>
       </c>
     </row>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:00</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:24</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:01</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:25</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:02</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:26</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:03</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:27</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:04</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:28</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:05</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:29</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:06</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:30</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:07</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:31</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:08</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:32</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:09</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:33</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16672,7 +16672,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:10</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:11</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:11</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:11</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:11</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:11</t>
+          <t>2026-03-12 09:04:34</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:12</t>
+          <t>2026-03-12 09:04:36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:14</t>
+          <t>2026-03-12 09:04:37</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:15</t>
+          <t>2026-03-12 09:04:38</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -17159,7 +17159,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:16</t>
+          <t>2026-03-12 09:04:39</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:18</t>
+          <t>2026-03-12 09:04:42</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:19</t>
+          <t>2026-03-12 09:04:42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:19</t>
+          <t>2026-03-12 09:04:42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:19</t>
+          <t>2026-03-12 09:04:42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:19</t>
+          <t>2026-03-12 09:04:43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:20</t>
+          <t>2026-03-12 09:04:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:20</t>
+          <t>2026-03-12 09:04:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:20</t>
+          <t>2026-03-12 09:04:44</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:21</t>
+          <t>2026-03-12 09:04:44</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:21</t>
+          <t>2026-03-12 09:04:44</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:21</t>
+          <t>2026-03-12 09:04:45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -17859,7 +17859,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:22</t>
+          <t>2026-03-12 09:04:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:22</t>
+          <t>2026-03-12 09:04:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:22</t>
+          <t>2026-03-12 09:04:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:23</t>
+          <t>2026-03-12 09:04:46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:23</t>
+          <t>2026-03-12 09:04:46</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -18069,7 +18069,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:24</t>
+          <t>2026-03-12 09:04:47</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:24</t>
+          <t>2026-03-12 09:04:47</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:24</t>
+          <t>2026-03-12 09:04:47</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:25</t>
+          <t>2026-03-12 09:04:48</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:25</t>
+          <t>2026-03-12 09:04:48</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -18279,7 +18279,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:25</t>
+          <t>2026-03-12 09:04:48</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:25</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:26</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:27</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -18879,7 +18879,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:27</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:27</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:27</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19005,7 +19005,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:56:27</t>
+          <t>2026-03-12 09:04:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Test Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Full Register Scan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +84,36 @@
       <color rgb="00222222"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -131,8 +160,38 @@
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003D3D3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00555555"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D5700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -168,11 +227,55 @@
         <color rgb="009DA7C7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009DA7C7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009DA7C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DA7C7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009DA7C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DA7C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009DA7C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DA7C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DA7C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +325,35 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -974,6 +1106,13 @@
           <t>Device Identity (Table A)</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="20" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="15" t="inlineStr"/>
@@ -1247,6 +1386,13 @@
           <t>§9.5  Status / Alarms / Triggers</t>
         </is>
       </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="20" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="15" t="inlineStr"/>
@@ -1900,6 +2046,13 @@
           <t>§9.6  General Module Configuration</t>
         </is>
       </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="20" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="15" t="inlineStr"/>
@@ -2477,6 +2630,13 @@
           <t>§9.7  Fine Tune / Frequency Limits</t>
         </is>
       </c>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="20" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="15" t="inlineStr"/>
@@ -2902,6 +3062,13 @@
           <t>§9.8  Health / Dither / Age</t>
         </is>
       </c>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="19" t="n"/>
+      <c r="G58" s="19" t="n"/>
+      <c r="H58" s="20" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="15" t="inlineStr"/>
@@ -3365,6 +3532,13 @@
           <t>§9.9  Manufacturer-Specific</t>
         </is>
       </c>
+      <c r="B71" s="19" t="n"/>
+      <c r="C71" s="19" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="19" t="n"/>
+      <c r="G71" s="19" t="n"/>
+      <c r="H71" s="20" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="15" t="inlineStr"/>
@@ -4125,4 +4299,7280 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F260"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Full Register Scan — 0x00 to 0xFF (256 Registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tester: Rishi   |   Date: 2026-03-12 09:04   |   Interface: UART /dev/ttyUSB0 @ 115200 baud   |   89 implemented, 167 reserved/not implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL: 256</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED: 89</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>NOT IMPL: 167</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>PASS: 88</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>FAIL: 1 *</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>* 0x13 fixed in latest firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Read Value</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>0x8000</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>0x01</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>0x0008</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>0x02</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>0x0010</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>0x03</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>0x04</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>0x05</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>0x000B</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>0x06</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>0x0006</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>0x07</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>0x0006</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>0x08</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>0x09</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>0x0A</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>0x0B</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>0x312E</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>0x0C</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr"/>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>0x0D</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>0x0E</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>0x0F</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>0x10</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>0x312E</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>0x11</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>0x12</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>0x13</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>* Fixed in latest firmware</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>0x14</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>0x15</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>0x16</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>0x17</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr"/>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr"/>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>0x19</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr"/>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>0x1A</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>0x1B</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr"/>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>0x1C</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr"/>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>0x1D</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr"/>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>0x1E</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="28" t="inlineStr"/>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>0x1F</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr"/>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>0xD080</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>0xD585</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>0x24</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>0x25</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>0x26</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>0x1FBF</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>0x000F</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>0x0D0D</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>0x2B</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="28" t="inlineStr"/>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>0x2C</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="inlineStr"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>0x2D</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>0x2E</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="inlineStr"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>0x2F</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>0x30</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>0x31</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>0x32</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>0x33</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>0x0002</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>0x34</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>0x01F4</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>0x35</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>0x00C1</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>0x37</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D60" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="28" t="inlineStr"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E61" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="28" t="inlineStr"/>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>0x39</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E62" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="28" t="inlineStr"/>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D63" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="28" t="inlineStr"/>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>0x3B</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="28" t="inlineStr"/>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>0x3C</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D65" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="inlineStr"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>0x3D</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E66" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="28" t="inlineStr"/>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>0x3E</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr"/>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>0x3F</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D68" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E68" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="28" t="inlineStr"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>0x00C1</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>0x42</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>0x43</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>0x09C4</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="28" t="inlineStr"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="28" t="inlineStr"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>0x46</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D75" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="28" t="inlineStr"/>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D76" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E76" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="28" t="inlineStr"/>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D77" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="28" t="inlineStr"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>0x49</t>
+        </is>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D78" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="28" t="inlineStr"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>0x4A</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D79" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="28" t="inlineStr"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>0x4B</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D80" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="28" t="inlineStr"/>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>0x4C</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D81" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="28" t="inlineStr"/>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>0x4D</t>
+        </is>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D82" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="28" t="inlineStr"/>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>0x4E</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D83" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="28" t="inlineStr"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>0x4F</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>0x1388</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>0x50</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>0x07D0</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>0x00C1</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>0x54</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>0x00C6</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>0x55</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>0x56</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>0x00FA</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr"/>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>0x57</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>0x0008</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>0x58</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>0x0004</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>0x5A</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>0x5B</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>0xFE0C</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>0x5E</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>0x1B58</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>0x63</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>0x64</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>0x65</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>0x66</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="16" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>0x68</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr"/>
+    </row>
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="16" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>0x6A</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>0x6C</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D113" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E113" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="28" t="inlineStr"/>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>0x6D</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D114" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E114" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="28" t="inlineStr"/>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>0x6E</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D115" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="28" t="inlineStr"/>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>0x6F</t>
+        </is>
+      </c>
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D116" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="28" t="inlineStr"/>
+    </row>
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="27" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D117" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="28" t="inlineStr"/>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>0x71</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D118" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E118" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="28" t="inlineStr"/>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>0x72</t>
+        </is>
+      </c>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D119" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E119" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="28" t="inlineStr"/>
+    </row>
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="27" t="inlineStr">
+        <is>
+          <t>0x73</t>
+        </is>
+      </c>
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D120" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E120" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" s="28" t="inlineStr"/>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>0x74</t>
+        </is>
+      </c>
+      <c r="B121" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D121" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E121" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="28" t="inlineStr"/>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>0x75</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D122" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E122" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="28" t="inlineStr"/>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D123" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E123" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="28" t="inlineStr"/>
+    </row>
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C124" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D124" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E124" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F124" s="28" t="inlineStr"/>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>0x78</t>
+        </is>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D125" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F125" s="28" t="inlineStr"/>
+    </row>
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t>0x79</t>
+        </is>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C126" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D126" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E126" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="28" t="inlineStr"/>
+    </row>
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>0x7A</t>
+        </is>
+      </c>
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D127" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E127" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F127" s="28" t="inlineStr"/>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>0x7B</t>
+        </is>
+      </c>
+      <c r="B128" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C128" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D128" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E128" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" s="28" t="inlineStr"/>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
+        <is>
+          <t>0x7C</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C129" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D129" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E129" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="28" t="inlineStr"/>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="27" t="inlineStr">
+        <is>
+          <t>0x7D</t>
+        </is>
+      </c>
+      <c r="B130" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C130" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D130" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E130" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" s="28" t="inlineStr"/>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t>0x7E</t>
+        </is>
+      </c>
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D131" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E131" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="28" t="inlineStr"/>
+    </row>
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="27" t="inlineStr">
+        <is>
+          <t>0x7F</t>
+        </is>
+      </c>
+      <c r="B132" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C132" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D132" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E132" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F132" s="28" t="inlineStr"/>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>0x80</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>0x81</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>0x82</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr"/>
+    </row>
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>0x83</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>0x84</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr"/>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>0x85</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>0x86</t>
+        </is>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="16" t="inlineStr">
+        <is>
+          <t>0x87</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>0x88</t>
+        </is>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr"/>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="16" t="inlineStr">
+        <is>
+          <t>0x89</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>0x8A</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr"/>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="16" t="inlineStr">
+        <is>
+          <t>0x8B</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>0x8C</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr"/>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t>0x8D</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>0x8E</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr"/>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>0x8F</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>0x90</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr"/>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>0x92</t>
+        </is>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr"/>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="27" t="inlineStr">
+        <is>
+          <t>0x93</t>
+        </is>
+      </c>
+      <c r="B152" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C152" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D152" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E152" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" s="28" t="inlineStr"/>
+    </row>
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="27" t="inlineStr">
+        <is>
+          <t>0x94</t>
+        </is>
+      </c>
+      <c r="B153" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C153" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D153" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E153" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" s="28" t="inlineStr"/>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="27" t="inlineStr">
+        <is>
+          <t>0x95</t>
+        </is>
+      </c>
+      <c r="B154" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C154" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D154" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E154" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" s="28" t="inlineStr"/>
+    </row>
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="27" t="inlineStr">
+        <is>
+          <t>0x96</t>
+        </is>
+      </c>
+      <c r="B155" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C155" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D155" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E155" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="28" t="inlineStr"/>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="27" t="inlineStr">
+        <is>
+          <t>0x97</t>
+        </is>
+      </c>
+      <c r="B156" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C156" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D156" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E156" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" s="28" t="inlineStr"/>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="27" t="inlineStr">
+        <is>
+          <t>0x98</t>
+        </is>
+      </c>
+      <c r="B157" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C157" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D157" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E157" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="28" t="inlineStr"/>
+    </row>
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="27" t="inlineStr">
+        <is>
+          <t>0x99</t>
+        </is>
+      </c>
+      <c r="B158" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C158" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D158" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E158" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="28" t="inlineStr"/>
+    </row>
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="27" t="inlineStr">
+        <is>
+          <t>0x9A</t>
+        </is>
+      </c>
+      <c r="B159" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C159" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D159" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E159" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" s="28" t="inlineStr"/>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="27" t="inlineStr">
+        <is>
+          <t>0x9B</t>
+        </is>
+      </c>
+      <c r="B160" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C160" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D160" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E160" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" s="28" t="inlineStr"/>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="27" t="inlineStr">
+        <is>
+          <t>0x9C</t>
+        </is>
+      </c>
+      <c r="B161" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C161" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D161" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E161" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F161" s="28" t="inlineStr"/>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="27" t="inlineStr">
+        <is>
+          <t>0x9D</t>
+        </is>
+      </c>
+      <c r="B162" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C162" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D162" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E162" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F162" s="28" t="inlineStr"/>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="27" t="inlineStr">
+        <is>
+          <t>0x9E</t>
+        </is>
+      </c>
+      <c r="B163" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C163" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D163" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E163" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" s="28" t="inlineStr"/>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="27" t="inlineStr">
+        <is>
+          <t>0x9F</t>
+        </is>
+      </c>
+      <c r="B164" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C164" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D164" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E164" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F164" s="28" t="inlineStr"/>
+    </row>
+    <row r="165" ht="14" customHeight="1">
+      <c r="A165" s="27" t="inlineStr">
+        <is>
+          <t>0xA0</t>
+        </is>
+      </c>
+      <c r="B165" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C165" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D165" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E165" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F165" s="28" t="inlineStr"/>
+    </row>
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="27" t="inlineStr">
+        <is>
+          <t>0xA1</t>
+        </is>
+      </c>
+      <c r="B166" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C166" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D166" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E166" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F166" s="28" t="inlineStr"/>
+    </row>
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="27" t="inlineStr">
+        <is>
+          <t>0xA2</t>
+        </is>
+      </c>
+      <c r="B167" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C167" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D167" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E167" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F167" s="28" t="inlineStr"/>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="27" t="inlineStr">
+        <is>
+          <t>0xA3</t>
+        </is>
+      </c>
+      <c r="B168" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C168" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D168" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E168" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F168" s="28" t="inlineStr"/>
+    </row>
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="27" t="inlineStr">
+        <is>
+          <t>0xA4</t>
+        </is>
+      </c>
+      <c r="B169" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C169" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D169" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E169" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" s="28" t="inlineStr"/>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="27" t="inlineStr">
+        <is>
+          <t>0xA5</t>
+        </is>
+      </c>
+      <c r="B170" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C170" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D170" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E170" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" s="28" t="inlineStr"/>
+    </row>
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="27" t="inlineStr">
+        <is>
+          <t>0xA6</t>
+        </is>
+      </c>
+      <c r="B171" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C171" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D171" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E171" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F171" s="28" t="inlineStr"/>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="27" t="inlineStr">
+        <is>
+          <t>0xA7</t>
+        </is>
+      </c>
+      <c r="B172" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C172" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D172" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E172" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F172" s="28" t="inlineStr"/>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="27" t="inlineStr">
+        <is>
+          <t>0xA8</t>
+        </is>
+      </c>
+      <c r="B173" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C173" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D173" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E173" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" s="28" t="inlineStr"/>
+    </row>
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="27" t="inlineStr">
+        <is>
+          <t>0xA9</t>
+        </is>
+      </c>
+      <c r="B174" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C174" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D174" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E174" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="28" t="inlineStr"/>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="27" t="inlineStr">
+        <is>
+          <t>0xAA</t>
+        </is>
+      </c>
+      <c r="B175" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C175" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D175" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E175" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="28" t="inlineStr"/>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="27" t="inlineStr">
+        <is>
+          <t>0xAB</t>
+        </is>
+      </c>
+      <c r="B176" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C176" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D176" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E176" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="28" t="inlineStr"/>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="27" t="inlineStr">
+        <is>
+          <t>0xAC</t>
+        </is>
+      </c>
+      <c r="B177" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C177" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D177" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E177" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="28" t="inlineStr"/>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="27" t="inlineStr">
+        <is>
+          <t>0xAD</t>
+        </is>
+      </c>
+      <c r="B178" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C178" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D178" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E178" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" s="28" t="inlineStr"/>
+    </row>
+    <row r="179" ht="14" customHeight="1">
+      <c r="A179" s="27" t="inlineStr">
+        <is>
+          <t>0xAE</t>
+        </is>
+      </c>
+      <c r="B179" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C179" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D179" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E179" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" s="28" t="inlineStr"/>
+    </row>
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="27" t="inlineStr">
+        <is>
+          <t>0xAF</t>
+        </is>
+      </c>
+      <c r="B180" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C180" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D180" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E180" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" s="28" t="inlineStr"/>
+    </row>
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="27" t="inlineStr">
+        <is>
+          <t>0xB0</t>
+        </is>
+      </c>
+      <c r="B181" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C181" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D181" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E181" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" s="28" t="inlineStr"/>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="27" t="inlineStr">
+        <is>
+          <t>0xB1</t>
+        </is>
+      </c>
+      <c r="B182" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C182" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D182" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E182" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" s="28" t="inlineStr"/>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="27" t="inlineStr">
+        <is>
+          <t>0xB2</t>
+        </is>
+      </c>
+      <c r="B183" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C183" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D183" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E183" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F183" s="28" t="inlineStr"/>
+    </row>
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="27" t="inlineStr">
+        <is>
+          <t>0xB3</t>
+        </is>
+      </c>
+      <c r="B184" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C184" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D184" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E184" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" s="28" t="inlineStr"/>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="27" t="inlineStr">
+        <is>
+          <t>0xB4</t>
+        </is>
+      </c>
+      <c r="B185" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C185" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D185" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E185" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F185" s="28" t="inlineStr"/>
+    </row>
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="27" t="inlineStr">
+        <is>
+          <t>0xB5</t>
+        </is>
+      </c>
+      <c r="B186" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C186" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D186" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E186" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" s="28" t="inlineStr"/>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="27" t="inlineStr">
+        <is>
+          <t>0xB6</t>
+        </is>
+      </c>
+      <c r="B187" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C187" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D187" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E187" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" s="28" t="inlineStr"/>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="27" t="inlineStr">
+        <is>
+          <t>0xB7</t>
+        </is>
+      </c>
+      <c r="B188" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C188" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D188" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E188" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" s="28" t="inlineStr"/>
+    </row>
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="27" t="inlineStr">
+        <is>
+          <t>0xB8</t>
+        </is>
+      </c>
+      <c r="B189" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C189" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D189" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E189" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F189" s="28" t="inlineStr"/>
+    </row>
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="27" t="inlineStr">
+        <is>
+          <t>0xB9</t>
+        </is>
+      </c>
+      <c r="B190" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C190" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D190" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E190" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" s="28" t="inlineStr"/>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="27" t="inlineStr">
+        <is>
+          <t>0xBA</t>
+        </is>
+      </c>
+      <c r="B191" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C191" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D191" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E191" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="28" t="inlineStr"/>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="27" t="inlineStr">
+        <is>
+          <t>0xBB</t>
+        </is>
+      </c>
+      <c r="B192" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C192" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D192" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E192" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" s="28" t="inlineStr"/>
+    </row>
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="27" t="inlineStr">
+        <is>
+          <t>0xBC</t>
+        </is>
+      </c>
+      <c r="B193" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C193" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D193" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E193" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" s="28" t="inlineStr"/>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="27" t="inlineStr">
+        <is>
+          <t>0xBD</t>
+        </is>
+      </c>
+      <c r="B194" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C194" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D194" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E194" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F194" s="28" t="inlineStr"/>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="27" t="inlineStr">
+        <is>
+          <t>0xBE</t>
+        </is>
+      </c>
+      <c r="B195" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C195" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D195" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E195" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F195" s="28" t="inlineStr"/>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="27" t="inlineStr">
+        <is>
+          <t>0xBF</t>
+        </is>
+      </c>
+      <c r="B196" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C196" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D196" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E196" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" s="28" t="inlineStr"/>
+    </row>
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="27" t="inlineStr">
+        <is>
+          <t>0xC0</t>
+        </is>
+      </c>
+      <c r="B197" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C197" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D197" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E197" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F197" s="28" t="inlineStr"/>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="27" t="inlineStr">
+        <is>
+          <t>0xC1</t>
+        </is>
+      </c>
+      <c r="B198" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C198" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D198" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E198" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F198" s="28" t="inlineStr"/>
+    </row>
+    <row r="199" ht="14" customHeight="1">
+      <c r="A199" s="27" t="inlineStr">
+        <is>
+          <t>0xC2</t>
+        </is>
+      </c>
+      <c r="B199" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C199" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D199" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E199" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" s="28" t="inlineStr"/>
+    </row>
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="27" t="inlineStr">
+        <is>
+          <t>0xC3</t>
+        </is>
+      </c>
+      <c r="B200" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C200" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D200" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E200" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" s="28" t="inlineStr"/>
+    </row>
+    <row r="201" ht="14" customHeight="1">
+      <c r="A201" s="27" t="inlineStr">
+        <is>
+          <t>0xC4</t>
+        </is>
+      </c>
+      <c r="B201" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C201" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D201" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E201" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" s="28" t="inlineStr"/>
+    </row>
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="27" t="inlineStr">
+        <is>
+          <t>0xC5</t>
+        </is>
+      </c>
+      <c r="B202" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C202" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D202" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E202" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" s="28" t="inlineStr"/>
+    </row>
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="27" t="inlineStr">
+        <is>
+          <t>0xC6</t>
+        </is>
+      </c>
+      <c r="B203" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C203" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D203" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E203" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" s="28" t="inlineStr"/>
+    </row>
+    <row r="204" ht="14" customHeight="1">
+      <c r="A204" s="27" t="inlineStr">
+        <is>
+          <t>0xC7</t>
+        </is>
+      </c>
+      <c r="B204" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C204" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D204" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E204" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" s="28" t="inlineStr"/>
+    </row>
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="27" t="inlineStr">
+        <is>
+          <t>0xC8</t>
+        </is>
+      </c>
+      <c r="B205" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C205" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D205" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E205" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" s="28" t="inlineStr"/>
+    </row>
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="27" t="inlineStr">
+        <is>
+          <t>0xC9</t>
+        </is>
+      </c>
+      <c r="B206" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C206" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D206" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E206" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" s="28" t="inlineStr"/>
+    </row>
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="27" t="inlineStr">
+        <is>
+          <t>0xCA</t>
+        </is>
+      </c>
+      <c r="B207" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C207" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D207" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E207" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F207" s="28" t="inlineStr"/>
+    </row>
+    <row r="208" ht="14" customHeight="1">
+      <c r="A208" s="27" t="inlineStr">
+        <is>
+          <t>0xCB</t>
+        </is>
+      </c>
+      <c r="B208" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C208" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D208" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E208" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" s="28" t="inlineStr"/>
+    </row>
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="27" t="inlineStr">
+        <is>
+          <t>0xCC</t>
+        </is>
+      </c>
+      <c r="B209" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C209" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D209" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E209" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" s="28" t="inlineStr"/>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="27" t="inlineStr">
+        <is>
+          <t>0xCD</t>
+        </is>
+      </c>
+      <c r="B210" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C210" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D210" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E210" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F210" s="28" t="inlineStr"/>
+    </row>
+    <row r="211" ht="14" customHeight="1">
+      <c r="A211" s="27" t="inlineStr">
+        <is>
+          <t>0xCE</t>
+        </is>
+      </c>
+      <c r="B211" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C211" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D211" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E211" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F211" s="28" t="inlineStr"/>
+    </row>
+    <row r="212" ht="14" customHeight="1">
+      <c r="A212" s="27" t="inlineStr">
+        <is>
+          <t>0xCF</t>
+        </is>
+      </c>
+      <c r="B212" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C212" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D212" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E212" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F212" s="28" t="inlineStr"/>
+    </row>
+    <row r="213" ht="14" customHeight="1">
+      <c r="A213" s="27" t="inlineStr">
+        <is>
+          <t>0xD0</t>
+        </is>
+      </c>
+      <c r="B213" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C213" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D213" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E213" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F213" s="28" t="inlineStr"/>
+    </row>
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="27" t="inlineStr">
+        <is>
+          <t>0xD1</t>
+        </is>
+      </c>
+      <c r="B214" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C214" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D214" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E214" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F214" s="28" t="inlineStr"/>
+    </row>
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="27" t="inlineStr">
+        <is>
+          <t>0xD2</t>
+        </is>
+      </c>
+      <c r="B215" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C215" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D215" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E215" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F215" s="28" t="inlineStr"/>
+    </row>
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="27" t="inlineStr">
+        <is>
+          <t>0xD3</t>
+        </is>
+      </c>
+      <c r="B216" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C216" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D216" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E216" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F216" s="28" t="inlineStr"/>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="27" t="inlineStr">
+        <is>
+          <t>0xD4</t>
+        </is>
+      </c>
+      <c r="B217" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C217" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D217" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E217" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F217" s="28" t="inlineStr"/>
+    </row>
+    <row r="218" ht="14" customHeight="1">
+      <c r="A218" s="27" t="inlineStr">
+        <is>
+          <t>0xD5</t>
+        </is>
+      </c>
+      <c r="B218" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C218" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D218" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E218" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" s="28" t="inlineStr"/>
+    </row>
+    <row r="219" ht="14" customHeight="1">
+      <c r="A219" s="27" t="inlineStr">
+        <is>
+          <t>0xD6</t>
+        </is>
+      </c>
+      <c r="B219" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C219" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D219" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E219" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" s="28" t="inlineStr"/>
+    </row>
+    <row r="220" ht="14" customHeight="1">
+      <c r="A220" s="27" t="inlineStr">
+        <is>
+          <t>0xD7</t>
+        </is>
+      </c>
+      <c r="B220" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C220" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D220" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E220" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" s="28" t="inlineStr"/>
+    </row>
+    <row r="221" ht="14" customHeight="1">
+      <c r="A221" s="27" t="inlineStr">
+        <is>
+          <t>0xD8</t>
+        </is>
+      </c>
+      <c r="B221" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C221" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D221" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E221" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" s="28" t="inlineStr"/>
+    </row>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="27" t="inlineStr">
+        <is>
+          <t>0xD9</t>
+        </is>
+      </c>
+      <c r="B222" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C222" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D222" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E222" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F222" s="28" t="inlineStr"/>
+    </row>
+    <row r="223" ht="14" customHeight="1">
+      <c r="A223" s="27" t="inlineStr">
+        <is>
+          <t>0xDA</t>
+        </is>
+      </c>
+      <c r="B223" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C223" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D223" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E223" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F223" s="28" t="inlineStr"/>
+    </row>
+    <row r="224" ht="14" customHeight="1">
+      <c r="A224" s="27" t="inlineStr">
+        <is>
+          <t>0xDB</t>
+        </is>
+      </c>
+      <c r="B224" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C224" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D224" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E224" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F224" s="28" t="inlineStr"/>
+    </row>
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="27" t="inlineStr">
+        <is>
+          <t>0xDC</t>
+        </is>
+      </c>
+      <c r="B225" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C225" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D225" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E225" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F225" s="28" t="inlineStr"/>
+    </row>
+    <row r="226" ht="14" customHeight="1">
+      <c r="A226" s="27" t="inlineStr">
+        <is>
+          <t>0xDD</t>
+        </is>
+      </c>
+      <c r="B226" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C226" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D226" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E226" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F226" s="28" t="inlineStr"/>
+    </row>
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="27" t="inlineStr">
+        <is>
+          <t>0xDE</t>
+        </is>
+      </c>
+      <c r="B227" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C227" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D227" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E227" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F227" s="28" t="inlineStr"/>
+    </row>
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="27" t="inlineStr">
+        <is>
+          <t>0xDF</t>
+        </is>
+      </c>
+      <c r="B228" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C228" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D228" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E228" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F228" s="28" t="inlineStr"/>
+    </row>
+    <row r="229" ht="14" customHeight="1">
+      <c r="A229" s="27" t="inlineStr">
+        <is>
+          <t>0xE0</t>
+        </is>
+      </c>
+      <c r="B229" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C229" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D229" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E229" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" s="28" t="inlineStr"/>
+    </row>
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="27" t="inlineStr">
+        <is>
+          <t>0xE1</t>
+        </is>
+      </c>
+      <c r="B230" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C230" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D230" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E230" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F230" s="28" t="inlineStr"/>
+    </row>
+    <row r="231" ht="14" customHeight="1">
+      <c r="A231" s="27" t="inlineStr">
+        <is>
+          <t>0xE2</t>
+        </is>
+      </c>
+      <c r="B231" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C231" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D231" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E231" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F231" s="28" t="inlineStr"/>
+    </row>
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="27" t="inlineStr">
+        <is>
+          <t>0xE3</t>
+        </is>
+      </c>
+      <c r="B232" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C232" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D232" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E232" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F232" s="28" t="inlineStr"/>
+    </row>
+    <row r="233" ht="14" customHeight="1">
+      <c r="A233" s="27" t="inlineStr">
+        <is>
+          <t>0xE4</t>
+        </is>
+      </c>
+      <c r="B233" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C233" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D233" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E233" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F233" s="28" t="inlineStr"/>
+    </row>
+    <row r="234" ht="14" customHeight="1">
+      <c r="A234" s="27" t="inlineStr">
+        <is>
+          <t>0xE5</t>
+        </is>
+      </c>
+      <c r="B234" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C234" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D234" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E234" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F234" s="28" t="inlineStr"/>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="27" t="inlineStr">
+        <is>
+          <t>0xE6</t>
+        </is>
+      </c>
+      <c r="B235" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C235" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D235" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E235" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F235" s="28" t="inlineStr"/>
+    </row>
+    <row r="236" ht="14" customHeight="1">
+      <c r="A236" s="27" t="inlineStr">
+        <is>
+          <t>0xE7</t>
+        </is>
+      </c>
+      <c r="B236" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C236" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D236" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E236" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F236" s="28" t="inlineStr"/>
+    </row>
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="27" t="inlineStr">
+        <is>
+          <t>0xE8</t>
+        </is>
+      </c>
+      <c r="B237" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C237" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D237" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E237" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F237" s="28" t="inlineStr"/>
+    </row>
+    <row r="238" ht="14" customHeight="1">
+      <c r="A238" s="27" t="inlineStr">
+        <is>
+          <t>0xE9</t>
+        </is>
+      </c>
+      <c r="B238" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C238" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D238" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E238" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F238" s="28" t="inlineStr"/>
+    </row>
+    <row r="239" ht="14" customHeight="1">
+      <c r="A239" s="27" t="inlineStr">
+        <is>
+          <t>0xEA</t>
+        </is>
+      </c>
+      <c r="B239" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C239" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D239" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E239" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F239" s="28" t="inlineStr"/>
+    </row>
+    <row r="240" ht="14" customHeight="1">
+      <c r="A240" s="27" t="inlineStr">
+        <is>
+          <t>0xEB</t>
+        </is>
+      </c>
+      <c r="B240" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C240" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D240" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E240" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F240" s="28" t="inlineStr"/>
+    </row>
+    <row r="241" ht="14" customHeight="1">
+      <c r="A241" s="27" t="inlineStr">
+        <is>
+          <t>0xEC</t>
+        </is>
+      </c>
+      <c r="B241" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C241" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D241" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E241" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F241" s="28" t="inlineStr"/>
+    </row>
+    <row r="242" ht="14" customHeight="1">
+      <c r="A242" s="27" t="inlineStr">
+        <is>
+          <t>0xED</t>
+        </is>
+      </c>
+      <c r="B242" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C242" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D242" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E242" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" s="28" t="inlineStr"/>
+    </row>
+    <row r="243" ht="14" customHeight="1">
+      <c r="A243" s="27" t="inlineStr">
+        <is>
+          <t>0xEE</t>
+        </is>
+      </c>
+      <c r="B243" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C243" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D243" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E243" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F243" s="28" t="inlineStr"/>
+    </row>
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="27" t="inlineStr">
+        <is>
+          <t>0xEF</t>
+        </is>
+      </c>
+      <c r="B244" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C244" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D244" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E244" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F244" s="28" t="inlineStr"/>
+    </row>
+    <row r="245" ht="14" customHeight="1">
+      <c r="A245" s="27" t="inlineStr">
+        <is>
+          <t>0xF0</t>
+        </is>
+      </c>
+      <c r="B245" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C245" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D245" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E245" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F245" s="28" t="inlineStr"/>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="27" t="inlineStr">
+        <is>
+          <t>0xF1</t>
+        </is>
+      </c>
+      <c r="B246" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C246" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D246" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E246" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F246" s="28" t="inlineStr"/>
+    </row>
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="27" t="inlineStr">
+        <is>
+          <t>0xF2</t>
+        </is>
+      </c>
+      <c r="B247" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C247" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D247" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E247" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F247" s="28" t="inlineStr"/>
+    </row>
+    <row r="248" ht="14" customHeight="1">
+      <c r="A248" s="27" t="inlineStr">
+        <is>
+          <t>0xF3</t>
+        </is>
+      </c>
+      <c r="B248" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C248" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D248" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E248" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F248" s="28" t="inlineStr"/>
+    </row>
+    <row r="249" ht="14" customHeight="1">
+      <c r="A249" s="27" t="inlineStr">
+        <is>
+          <t>0xF4</t>
+        </is>
+      </c>
+      <c r="B249" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C249" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D249" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E249" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F249" s="28" t="inlineStr"/>
+    </row>
+    <row r="250" ht="14" customHeight="1">
+      <c r="A250" s="27" t="inlineStr">
+        <is>
+          <t>0xF5</t>
+        </is>
+      </c>
+      <c r="B250" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C250" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D250" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E250" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F250" s="28" t="inlineStr"/>
+    </row>
+    <row r="251" ht="14" customHeight="1">
+      <c r="A251" s="27" t="inlineStr">
+        <is>
+          <t>0xF6</t>
+        </is>
+      </c>
+      <c r="B251" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C251" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D251" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E251" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" s="28" t="inlineStr"/>
+    </row>
+    <row r="252" ht="14" customHeight="1">
+      <c r="A252" s="27" t="inlineStr">
+        <is>
+          <t>0xF7</t>
+        </is>
+      </c>
+      <c r="B252" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C252" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D252" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E252" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F252" s="28" t="inlineStr"/>
+    </row>
+    <row r="253" ht="14" customHeight="1">
+      <c r="A253" s="27" t="inlineStr">
+        <is>
+          <t>0xF8</t>
+        </is>
+      </c>
+      <c r="B253" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C253" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D253" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E253" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F253" s="28" t="inlineStr"/>
+    </row>
+    <row r="254" ht="14" customHeight="1">
+      <c r="A254" s="27" t="inlineStr">
+        <is>
+          <t>0xF9</t>
+        </is>
+      </c>
+      <c r="B254" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C254" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D254" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E254" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F254" s="28" t="inlineStr"/>
+    </row>
+    <row r="255" ht="14" customHeight="1">
+      <c r="A255" s="27" t="inlineStr">
+        <is>
+          <t>0xFA</t>
+        </is>
+      </c>
+      <c r="B255" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C255" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D255" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E255" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F255" s="28" t="inlineStr"/>
+    </row>
+    <row r="256" ht="14" customHeight="1">
+      <c r="A256" s="27" t="inlineStr">
+        <is>
+          <t>0xFB</t>
+        </is>
+      </c>
+      <c r="B256" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C256" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D256" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E256" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F256" s="28" t="inlineStr"/>
+    </row>
+    <row r="257" ht="14" customHeight="1">
+      <c r="A257" s="27" t="inlineStr">
+        <is>
+          <t>0xFC</t>
+        </is>
+      </c>
+      <c r="B257" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C257" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D257" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E257" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F257" s="28" t="inlineStr"/>
+    </row>
+    <row r="258" ht="14" customHeight="1">
+      <c r="A258" s="27" t="inlineStr">
+        <is>
+          <t>0xFD</t>
+        </is>
+      </c>
+      <c r="B258" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C258" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D258" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E258" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F258" s="28" t="inlineStr"/>
+    </row>
+    <row r="259" ht="14" customHeight="1">
+      <c r="A259" s="27" t="inlineStr">
+        <is>
+          <t>0xFE</t>
+        </is>
+      </c>
+      <c r="B259" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C259" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D259" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E259" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F259" s="28" t="inlineStr"/>
+    </row>
+    <row r="260" ht="14" customHeight="1">
+      <c r="A260" s="27" t="inlineStr">
+        <is>
+          <t>0xFF</t>
+        </is>
+      </c>
+      <c r="B260" s="27" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="C260" s="28" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="D260" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E260" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F260" s="28" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dvt_excel.xlsx
+++ b/dvt_excel.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Test Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Full Register Scan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +84,14 @@
       <color rgb="00222222"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -131,6 +138,11 @@
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -172,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -223,6 +235,12 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4133,4 +4151,8268 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F259"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nano-ITLA — Full 256-Register Scan (0x00–0xFF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tester: Rishi   |   Date: 2026-03-12 09:04   |   Interface: UART /dev/ttyUSB0 @ 115200 baud   |   Device: Pilot Photonics nanoITLA-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Addr</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Hex</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Name / Description</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Raw Value</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>0x01</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Device Type</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>CW ITLA</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>0x02</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Pilot Photonics</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>0x03</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>NYITLA-01</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>0x04</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Serial Number</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>PP-000123</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>0x05</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Mfg Date</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>0x06</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>FW Release</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>0x07</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>FW Back-Level</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>0x08</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>0x09</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>0x0A</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>0x0B</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>0x0C</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>0x0D</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>0x0E</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>0x0F</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>0x10</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>NOOP</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>0x11</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>0x12</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>0x13</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>LstRsp</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>0x14</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>DL Config</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>0x15</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>DL Status</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>0x16</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>0x17</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>0x19</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>0x1A</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>0x1B</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>0x1C</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>0x1D</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>0x1E</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>0x1F</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>StatusF</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>0xD000</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>StatusW / COW</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>0xD505</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Fatal Pwr Thresh</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>0x0011</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Warn Pwr Thresh</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>0x0012</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>0x24</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Fatal Freq Th</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>0x0013</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>0x25</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Warn Freq Th</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>0x0014</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>0x26</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Fatal Therm Th</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>0x0015</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Warn Therm Th</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>0x0016</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>SRQ Triggers / Mask</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Fatal Triggers</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Alarm Mask</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>0x2B</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>0x2C</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>0x2D</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>0x2E</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>0x2F</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>0x30</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>0x0001</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>0x31</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>0x32</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>ResEna</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>0x33</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>MCB</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>0x0002</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>0x34</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Grid (G10)</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>0x01F4</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>0x35</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>FCF1 THz</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>0x00C1</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>FCF2 GHz×10</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>0x37</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>0x39</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>0x3B</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>0x3C</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>0x3D</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>0x3E</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>0x3F</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Laser Freq THz</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>0x00C1</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Laser Freq G10</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>0x42</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>LF1 Min THz</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>0x00BF</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>0x43</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>LF1 Max THz</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>0x00C4</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>0x46</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>0x49</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F77" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>0x4A</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F78" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>0x4B</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>0x4C</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>0x4D</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>0x4E</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>0x4F</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Min Freq THz</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="inlineStr">
+        <is>
+          <t>0x00BF</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>0x50</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Min Freq G10</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>0x1B58</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Max Freq THz</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="inlineStr">
+        <is>
+          <t>0x00C4</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Max Freq G10</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>0x1B58</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Min Power</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>0x54</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Last Freq THz</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>0x00C1</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>0x55</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Last Freq G10</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>0x1194</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>0x56</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Laser Grid G10</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>0x01F4</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>0x57</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Currents AEA</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>0x0008</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>0x58</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Temps AEA</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>0x0004</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Case Temp</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>0x5A</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Dither Period</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>0x5B</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Dither BW</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Device Cap 1</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Device Cap 2</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>0xFE0C</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>0x5E</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Device Cap 3</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>0x1B58</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Device Cap 4</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>FTF Min</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>0xCEC4</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Fine Tune Freq</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>0x63</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Fatal Freq Th2</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>0x0017</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>0x64</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Warn Freq Th2</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>0x0018</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>0x65</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Channel H</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>0x66</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Grid2 MHz</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>FCF3 MHz</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>0x68</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Laser Freq MHz</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Max Power</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>0x0514</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>0x6A</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Last Freq MHz</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Grid2 MHz (RO)</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E111" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>0x6C</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>0x6D</t>
+        </is>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C113" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F113" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="19" t="inlineStr">
+        <is>
+          <t>0x6E</t>
+        </is>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D114" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F114" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>0x6F</t>
+        </is>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C115" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F115" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="19" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D116" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F116" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>0x71</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F117" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="19" t="inlineStr">
+        <is>
+          <t>0x72</t>
+        </is>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D118" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F118" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>0x73</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F119" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="19" t="inlineStr">
+        <is>
+          <t>0x74</t>
+        </is>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D120" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>0x75</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F121" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="19" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D122" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F122" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F123" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>0x78</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D124" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>0x79</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
+          <t>0x7A</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>0x7B</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="19" t="inlineStr">
+        <is>
+          <t>0x7C</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D128" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="19" t="inlineStr">
+        <is>
+          <t>0x7D</t>
+        </is>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F129" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
+          <t>0x7E</t>
+        </is>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>0x7F</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F131" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>0x80</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Ring-1 Voltage</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>0x2706</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="16" t="inlineStr">
+        <is>
+          <t>0x81</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Ring-2 Voltage</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E133" s="16" t="inlineStr">
+        <is>
+          <t>0x15AE</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>0x82</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Phase Voltage</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>0x2F58</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="16" t="inlineStr">
+        <is>
+          <t>0x83</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Gain Bias</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>0x007B</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>0x84</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>SOA Current</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>0x007B</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="16" t="inlineStr">
+        <is>
+          <t>0x85</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>0xFE3E</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>0x86</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>Main PD (MPD)</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="16" t="inlineStr">
+        <is>
+          <t>0x87</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Etalon PD (WLPD)</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E139" s="16" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>0x88</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>WM PD (WMPD)</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>0x89</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>WM PD alias</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>0x8A</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>Etalon PD alias</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="16" t="inlineStr">
+        <is>
+          <t>0x8B</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Power PD alias</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>0x000A</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>0x8C</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Phase Tuner</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>0x2F58</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="16" t="inlineStr">
+        <is>
+          <t>0x8D</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Ring-1 Tuner</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>0x2706</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>0x8E</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Ring-2 Tuner</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>0x15AE</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>0x8F</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>SOA Tuner</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>0x007B</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>0x90</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Gain Bias Tuner</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>0x007B</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>TEC Raw</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>0xFFD3</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>0x92</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>0x0000</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="19" t="inlineStr">
+        <is>
+          <t>0x93</t>
+        </is>
+      </c>
+      <c r="B151" s="19" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C151" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D151" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t>0x94</t>
+        </is>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D152" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="19" t="inlineStr">
+        <is>
+          <t>0x95</t>
+        </is>
+      </c>
+      <c r="B153" s="19" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C153" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E153" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="19" t="inlineStr">
+        <is>
+          <t>0x96</t>
+        </is>
+      </c>
+      <c r="B154" s="19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="19" t="inlineStr">
+        <is>
+          <t>0x97</t>
+        </is>
+      </c>
+      <c r="B155" s="19" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C155" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D155" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="19" t="inlineStr">
+        <is>
+          <t>0x98</t>
+        </is>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D156" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="19" t="inlineStr">
+        <is>
+          <t>0x99</t>
+        </is>
+      </c>
+      <c r="B157" s="19" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C157" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D157" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="19" t="inlineStr">
+        <is>
+          <t>0x9A</t>
+        </is>
+      </c>
+      <c r="B158" s="19" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D158" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="19" t="inlineStr">
+        <is>
+          <t>0x9B</t>
+        </is>
+      </c>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C159" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D159" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="19" t="inlineStr">
+        <is>
+          <t>0x9C</t>
+        </is>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C160" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D160" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>0x9D</t>
+        </is>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C161" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D161" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F161" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="19" t="inlineStr">
+        <is>
+          <t>0x9E</t>
+        </is>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D162" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F162" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>0x9F</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="C163" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D163" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="19" t="inlineStr">
+        <is>
+          <t>0xA0</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D164" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="14" customHeight="1">
+      <c r="A165" s="19" t="inlineStr">
+        <is>
+          <t>0xA1</t>
+        </is>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C165" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D165" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E165" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F165" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="19" t="inlineStr">
+        <is>
+          <t>0xA2</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C166" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D166" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="19" t="inlineStr">
+        <is>
+          <t>0xA3</t>
+        </is>
+      </c>
+      <c r="B167" s="19" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C167" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D167" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F167" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="19" t="inlineStr">
+        <is>
+          <t>0xA4</t>
+        </is>
+      </c>
+      <c r="B168" s="19" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C168" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D168" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E168" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F168" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="19" t="inlineStr">
+        <is>
+          <t>0xA5</t>
+        </is>
+      </c>
+      <c r="B169" s="19" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="C169" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D169" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E169" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="19" t="inlineStr">
+        <is>
+          <t>0xA6</t>
+        </is>
+      </c>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D170" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E170" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="19" t="inlineStr">
+        <is>
+          <t>0xA7</t>
+        </is>
+      </c>
+      <c r="B171" s="19" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="C171" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D171" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F171" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>0xA8</t>
+        </is>
+      </c>
+      <c r="B172" s="19" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D172" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E172" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F172" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>0xA9</t>
+        </is>
+      </c>
+      <c r="B173" s="19" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="C173" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D173" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>0xAA</t>
+        </is>
+      </c>
+      <c r="B174" s="19" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D174" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E174" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>0xAB</t>
+        </is>
+      </c>
+      <c r="B175" s="19" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="C175" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D175" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>0xAC</t>
+        </is>
+      </c>
+      <c r="B176" s="19" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D176" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="19" t="inlineStr">
+        <is>
+          <t>0xAD</t>
+        </is>
+      </c>
+      <c r="B177" s="19" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="C177" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D177" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="19" t="inlineStr">
+        <is>
+          <t>0xAE</t>
+        </is>
+      </c>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="C178" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D178" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E178" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="14" customHeight="1">
+      <c r="A179" s="19" t="inlineStr">
+        <is>
+          <t>0xAF</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="C179" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D179" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="19" t="inlineStr">
+        <is>
+          <t>0xB0</t>
+        </is>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D180" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E180" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="19" t="inlineStr">
+        <is>
+          <t>0xB1</t>
+        </is>
+      </c>
+      <c r="B181" s="19" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="C181" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D181" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="19" t="inlineStr">
+        <is>
+          <t>0xB2</t>
+        </is>
+      </c>
+      <c r="B182" s="19" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="C182" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D182" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="19" t="inlineStr">
+        <is>
+          <t>0xB3</t>
+        </is>
+      </c>
+      <c r="B183" s="19" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="C183" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E183" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F183" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="19" t="inlineStr">
+        <is>
+          <t>0xB4</t>
+        </is>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C184" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D184" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E184" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="19" t="inlineStr">
+        <is>
+          <t>0xB5</t>
+        </is>
+      </c>
+      <c r="B185" s="19" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="C185" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E185" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F185" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="19" t="inlineStr">
+        <is>
+          <t>0xB6</t>
+        </is>
+      </c>
+      <c r="B186" s="19" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="C186" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D186" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E186" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="19" t="inlineStr">
+        <is>
+          <t>0xB7</t>
+        </is>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="C187" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D187" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E187" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="19" t="inlineStr">
+        <is>
+          <t>0xB8</t>
+        </is>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="C188" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D188" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E188" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="19" t="inlineStr">
+        <is>
+          <t>0xB9</t>
+        </is>
+      </c>
+      <c r="B189" s="19" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="C189" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D189" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E189" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F189" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="19" t="inlineStr">
+        <is>
+          <t>0xBA</t>
+        </is>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="C190" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D190" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E190" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="19" t="inlineStr">
+        <is>
+          <t>0xBB</t>
+        </is>
+      </c>
+      <c r="B191" s="19" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="C191" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D191" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E191" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="19" t="inlineStr">
+        <is>
+          <t>0xBC</t>
+        </is>
+      </c>
+      <c r="B192" s="19" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C192" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D192" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E192" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="19" t="inlineStr">
+        <is>
+          <t>0xBD</t>
+        </is>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C193" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D193" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E193" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="19" t="inlineStr">
+        <is>
+          <t>0xBE</t>
+        </is>
+      </c>
+      <c r="B194" s="19" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="C194" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D194" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E194" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F194" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="19" t="inlineStr">
+        <is>
+          <t>0xBF</t>
+        </is>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="C195" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D195" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E195" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F195" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="19" t="inlineStr">
+        <is>
+          <t>0xC0</t>
+        </is>
+      </c>
+      <c r="B196" s="19" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C196" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D196" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E196" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="19" t="inlineStr">
+        <is>
+          <t>0xC1</t>
+        </is>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="C197" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D197" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E197" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F197" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="19" t="inlineStr">
+        <is>
+          <t>0xC2</t>
+        </is>
+      </c>
+      <c r="B198" s="19" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="C198" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D198" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E198" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F198" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="14" customHeight="1">
+      <c r="A199" s="19" t="inlineStr">
+        <is>
+          <t>0xC3</t>
+        </is>
+      </c>
+      <c r="B199" s="19" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="C199" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D199" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E199" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="19" t="inlineStr">
+        <is>
+          <t>0xC4</t>
+        </is>
+      </c>
+      <c r="B200" s="19" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="C200" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D200" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="14" customHeight="1">
+      <c r="A201" s="19" t="inlineStr">
+        <is>
+          <t>0xC5</t>
+        </is>
+      </c>
+      <c r="B201" s="19" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="C201" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D201" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E201" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="19" t="inlineStr">
+        <is>
+          <t>0xC6</t>
+        </is>
+      </c>
+      <c r="B202" s="19" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="C202" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D202" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E202" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="19" t="inlineStr">
+        <is>
+          <t>0xC7</t>
+        </is>
+      </c>
+      <c r="B203" s="19" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="C203" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D203" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E203" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="14" customHeight="1">
+      <c r="A204" s="19" t="inlineStr">
+        <is>
+          <t>0xC8</t>
+        </is>
+      </c>
+      <c r="B204" s="19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C204" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D204" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E204" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="19" t="inlineStr">
+        <is>
+          <t>0xC9</t>
+        </is>
+      </c>
+      <c r="B205" s="19" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C205" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D205" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E205" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="19" t="inlineStr">
+        <is>
+          <t>0xCA</t>
+        </is>
+      </c>
+      <c r="B206" s="19" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C206" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D206" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E206" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="19" t="inlineStr">
+        <is>
+          <t>0xCB</t>
+        </is>
+      </c>
+      <c r="B207" s="19" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C207" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D207" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E207" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F207" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="14" customHeight="1">
+      <c r="A208" s="19" t="inlineStr">
+        <is>
+          <t>0xCC</t>
+        </is>
+      </c>
+      <c r="B208" s="19" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C208" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D208" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E208" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="19" t="inlineStr">
+        <is>
+          <t>0xCD</t>
+        </is>
+      </c>
+      <c r="B209" s="19" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="C209" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D209" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E209" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="19" t="inlineStr">
+        <is>
+          <t>0xCE</t>
+        </is>
+      </c>
+      <c r="B210" s="19" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C210" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D210" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E210" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F210" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="14" customHeight="1">
+      <c r="A211" s="19" t="inlineStr">
+        <is>
+          <t>0xCF</t>
+        </is>
+      </c>
+      <c r="B211" s="19" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C211" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D211" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E211" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F211" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="14" customHeight="1">
+      <c r="A212" s="19" t="inlineStr">
+        <is>
+          <t>0xD0</t>
+        </is>
+      </c>
+      <c r="B212" s="19" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C212" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D212" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E212" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F212" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="14" customHeight="1">
+      <c r="A213" s="19" t="inlineStr">
+        <is>
+          <t>0xD1</t>
+        </is>
+      </c>
+      <c r="B213" s="19" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C213" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D213" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E213" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F213" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="19" t="inlineStr">
+        <is>
+          <t>0xD2</t>
+        </is>
+      </c>
+      <c r="B214" s="19" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="C214" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D214" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E214" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F214" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="19" t="inlineStr">
+        <is>
+          <t>0xD3</t>
+        </is>
+      </c>
+      <c r="B215" s="19" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="C215" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D215" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E215" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F215" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="19" t="inlineStr">
+        <is>
+          <t>0xD4</t>
+        </is>
+      </c>
+      <c r="B216" s="19" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="C216" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D216" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E216" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F216" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="19" t="inlineStr">
+        <is>
+          <t>0xD5</t>
+        </is>
+      </c>
+      <c r="B217" s="19" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C217" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D217" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E217" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F217" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="14" customHeight="1">
+      <c r="A218" s="19" t="inlineStr">
+        <is>
+          <t>0xD6</t>
+        </is>
+      </c>
+      <c r="B218" s="19" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="C218" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D218" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E218" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="14" customHeight="1">
+      <c r="A219" s="19" t="inlineStr">
+        <is>
+          <t>0xD7</t>
+        </is>
+      </c>
+      <c r="B219" s="19" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="C219" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D219" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E219" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="14" customHeight="1">
+      <c r="A220" s="19" t="inlineStr">
+        <is>
+          <t>0xD8</t>
+        </is>
+      </c>
+      <c r="B220" s="19" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="C220" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D220" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E220" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="14" customHeight="1">
+      <c r="A221" s="19" t="inlineStr">
+        <is>
+          <t>0xD9</t>
+        </is>
+      </c>
+      <c r="B221" s="19" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="C221" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D221" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E221" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="19" t="inlineStr">
+        <is>
+          <t>0xDA</t>
+        </is>
+      </c>
+      <c r="B222" s="19" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="C222" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D222" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E222" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F222" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="14" customHeight="1">
+      <c r="A223" s="19" t="inlineStr">
+        <is>
+          <t>0xDB</t>
+        </is>
+      </c>
+      <c r="B223" s="19" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="C223" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D223" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E223" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F223" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="14" customHeight="1">
+      <c r="A224" s="19" t="inlineStr">
+        <is>
+          <t>0xDC</t>
+        </is>
+      </c>
+      <c r="B224" s="19" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C224" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D224" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E224" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F224" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="19" t="inlineStr">
+        <is>
+          <t>0xDD</t>
+        </is>
+      </c>
+      <c r="B225" s="19" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="C225" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D225" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E225" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F225" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="14" customHeight="1">
+      <c r="A226" s="19" t="inlineStr">
+        <is>
+          <t>0xDE</t>
+        </is>
+      </c>
+      <c r="B226" s="19" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C226" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D226" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E226" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F226" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="19" t="inlineStr">
+        <is>
+          <t>0xDF</t>
+        </is>
+      </c>
+      <c r="B227" s="19" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="C227" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D227" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E227" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F227" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="19" t="inlineStr">
+        <is>
+          <t>0xE0</t>
+        </is>
+      </c>
+      <c r="B228" s="19" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C228" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D228" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E228" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F228" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="14" customHeight="1">
+      <c r="A229" s="19" t="inlineStr">
+        <is>
+          <t>0xE1</t>
+        </is>
+      </c>
+      <c r="B229" s="19" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C229" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D229" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E229" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="19" t="inlineStr">
+        <is>
+          <t>0xE2</t>
+        </is>
+      </c>
+      <c r="B230" s="19" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C230" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D230" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E230" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F230" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="14" customHeight="1">
+      <c r="A231" s="19" t="inlineStr">
+        <is>
+          <t>0xE3</t>
+        </is>
+      </c>
+      <c r="B231" s="19" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="C231" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D231" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E231" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F231" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="19" t="inlineStr">
+        <is>
+          <t>0xE4</t>
+        </is>
+      </c>
+      <c r="B232" s="19" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C232" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D232" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E232" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F232" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="14" customHeight="1">
+      <c r="A233" s="19" t="inlineStr">
+        <is>
+          <t>0xE5</t>
+        </is>
+      </c>
+      <c r="B233" s="19" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C233" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D233" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E233" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F233" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="14" customHeight="1">
+      <c r="A234" s="19" t="inlineStr">
+        <is>
+          <t>0xE6</t>
+        </is>
+      </c>
+      <c r="B234" s="19" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C234" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D234" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E234" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F234" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="19" t="inlineStr">
+        <is>
+          <t>0xE7</t>
+        </is>
+      </c>
+      <c r="B235" s="19" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C235" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D235" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E235" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F235" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="14" customHeight="1">
+      <c r="A236" s="19" t="inlineStr">
+        <is>
+          <t>0xE8</t>
+        </is>
+      </c>
+      <c r="B236" s="19" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="C236" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D236" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E236" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F236" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="19" t="inlineStr">
+        <is>
+          <t>0xE9</t>
+        </is>
+      </c>
+      <c r="B237" s="19" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C237" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D237" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E237" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F237" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="14" customHeight="1">
+      <c r="A238" s="19" t="inlineStr">
+        <is>
+          <t>0xEA</t>
+        </is>
+      </c>
+      <c r="B238" s="19" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C238" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D238" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E238" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F238" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="14" customHeight="1">
+      <c r="A239" s="19" t="inlineStr">
+        <is>
+          <t>0xEB</t>
+        </is>
+      </c>
+      <c r="B239" s="19" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="C239" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D239" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E239" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F239" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="14" customHeight="1">
+      <c r="A240" s="19" t="inlineStr">
+        <is>
+          <t>0xEC</t>
+        </is>
+      </c>
+      <c r="B240" s="19" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C240" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D240" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E240" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F240" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="14" customHeight="1">
+      <c r="A241" s="19" t="inlineStr">
+        <is>
+          <t>0xED</t>
+        </is>
+      </c>
+      <c r="B241" s="19" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C241" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D241" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E241" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F241" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="14" customHeight="1">
+      <c r="A242" s="19" t="inlineStr">
+        <is>
+          <t>0xEE</t>
+        </is>
+      </c>
+      <c r="B242" s="19" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C242" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D242" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E242" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="14" customHeight="1">
+      <c r="A243" s="19" t="inlineStr">
+        <is>
+          <t>0xEF</t>
+        </is>
+      </c>
+      <c r="B243" s="19" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="C243" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D243" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E243" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F243" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="19" t="inlineStr">
+        <is>
+          <t>0xF0</t>
+        </is>
+      </c>
+      <c r="B244" s="19" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="C244" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D244" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E244" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F244" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="14" customHeight="1">
+      <c r="A245" s="19" t="inlineStr">
+        <is>
+          <t>0xF1</t>
+        </is>
+      </c>
+      <c r="B245" s="19" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="C245" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D245" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E245" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F245" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="19" t="inlineStr">
+        <is>
+          <t>0xF2</t>
+        </is>
+      </c>
+      <c r="B246" s="19" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C246" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D246" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E246" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F246" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="19" t="inlineStr">
+        <is>
+          <t>0xF3</t>
+        </is>
+      </c>
+      <c r="B247" s="19" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C247" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D247" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E247" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F247" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="14" customHeight="1">
+      <c r="A248" s="19" t="inlineStr">
+        <is>
+          <t>0xF4</t>
+        </is>
+      </c>
+      <c r="B248" s="19" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C248" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D248" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E248" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F248" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="14" customHeight="1">
+      <c r="A249" s="19" t="inlineStr">
+        <is>
+          <t>0xF5</t>
+        </is>
+      </c>
+      <c r="B249" s="19" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C249" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D249" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E249" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F249" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="14" customHeight="1">
+      <c r="A250" s="19" t="inlineStr">
+        <is>
+          <t>0xF6</t>
+        </is>
+      </c>
+      <c r="B250" s="19" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C250" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D250" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E250" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F250" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="14" customHeight="1">
+      <c r="A251" s="19" t="inlineStr">
+        <is>
+          <t>0xF7</t>
+        </is>
+      </c>
+      <c r="B251" s="19" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C251" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D251" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E251" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="14" customHeight="1">
+      <c r="A252" s="19" t="inlineStr">
+        <is>
+          <t>0xF8</t>
+        </is>
+      </c>
+      <c r="B252" s="19" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C252" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D252" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E252" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F252" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="14" customHeight="1">
+      <c r="A253" s="19" t="inlineStr">
+        <is>
+          <t>0xF9</t>
+        </is>
+      </c>
+      <c r="B253" s="19" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C253" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D253" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E253" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F253" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="14" customHeight="1">
+      <c r="A254" s="19" t="inlineStr">
+        <is>
+          <t>0xFA</t>
+        </is>
+      </c>
+      <c r="B254" s="19" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C254" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D254" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E254" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F254" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="14" customHeight="1">
+      <c r="A255" s="19" t="inlineStr">
+        <is>
+          <t>0xFB</t>
+        </is>
+      </c>
+      <c r="B255" s="19" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C255" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D255" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E255" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F255" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="14" customHeight="1">
+      <c r="A256" s="19" t="inlineStr">
+        <is>
+          <t>0xFC</t>
+        </is>
+      </c>
+      <c r="B256" s="19" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C256" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D256" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E256" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F256" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="14" customHeight="1">
+      <c r="A257" s="19" t="inlineStr">
+        <is>
+          <t>0xFD</t>
+        </is>
+      </c>
+      <c r="B257" s="19" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C257" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D257" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E257" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F257" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="14" customHeight="1">
+      <c r="A258" s="19" t="inlineStr">
+        <is>
+          <t>0xFE</t>
+        </is>
+      </c>
+      <c r="B258" s="19" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C258" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D258" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E258" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F258" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="14" customHeight="1">
+      <c r="A259" s="19" t="inlineStr">
+        <is>
+          <t>0xFF</t>
+        </is>
+      </c>
+      <c r="B259" s="19" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C259" s="20" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D259" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E259" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F259" s="19" t="inlineStr">
+        <is>
+          <t>N/I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>